--- a/AAII_Financials/Yearly/TTDKY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TTDKY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -723,25 +723,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>14480600</v>
+        <v>14698700</v>
       </c>
       <c r="E8" s="3">
-        <v>12630100</v>
+        <v>12820300</v>
       </c>
       <c r="F8" s="3">
-        <v>9820600</v>
+        <v>9968500</v>
       </c>
       <c r="G8" s="3">
-        <v>9050600</v>
+        <v>9186900</v>
       </c>
       <c r="H8" s="3">
-        <v>9175200</v>
+        <v>9313400</v>
       </c>
       <c r="I8" s="3">
-        <v>8444400</v>
+        <v>8571600</v>
       </c>
       <c r="J8" s="3">
-        <v>7823600</v>
+        <v>7941500</v>
       </c>
       <c r="K8" s="3">
         <v>8469100</v>
@@ -765,25 +765,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>10599400</v>
+        <v>10759000</v>
       </c>
       <c r="E9" s="3">
-        <v>8886200</v>
+        <v>9020000</v>
       </c>
       <c r="F9" s="3">
-        <v>6988000</v>
+        <v>7093200</v>
       </c>
       <c r="G9" s="3">
-        <v>6372500</v>
+        <v>6468500</v>
       </c>
       <c r="H9" s="3">
-        <v>6542500</v>
+        <v>6641100</v>
       </c>
       <c r="I9" s="3">
-        <v>6165400</v>
+        <v>6258300</v>
       </c>
       <c r="J9" s="3">
-        <v>5683500</v>
+        <v>5769100</v>
       </c>
       <c r="K9" s="3">
         <v>6108800</v>
@@ -807,25 +807,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3881200</v>
+        <v>3939700</v>
       </c>
       <c r="E10" s="3">
-        <v>3744000</v>
+        <v>3800300</v>
       </c>
       <c r="F10" s="3">
-        <v>2832600</v>
+        <v>2875300</v>
       </c>
       <c r="G10" s="3">
-        <v>2678100</v>
+        <v>2718400</v>
       </c>
       <c r="H10" s="3">
-        <v>2632700</v>
+        <v>2672300</v>
       </c>
       <c r="I10" s="3">
-        <v>2279000</v>
+        <v>2313300</v>
       </c>
       <c r="J10" s="3">
-        <v>2140100</v>
+        <v>2172400</v>
       </c>
       <c r="K10" s="3">
         <v>2360300</v>
@@ -951,16 +951,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-11900</v>
+        <v>-12100</v>
       </c>
       <c r="E14" s="3">
-        <v>-49700</v>
+        <v>-50400</v>
       </c>
       <c r="F14" s="3">
-        <v>9900</v>
+        <v>10000</v>
       </c>
       <c r="G14" s="3">
-        <v>132100</v>
+        <v>134100</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1050,25 +1050,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13359600</v>
+        <v>13560800</v>
       </c>
       <c r="E17" s="3">
-        <v>11522700</v>
+        <v>11696300</v>
       </c>
       <c r="F17" s="3">
-        <v>9078200</v>
+        <v>9214900</v>
       </c>
       <c r="G17" s="3">
-        <v>8409400</v>
+        <v>8536000</v>
       </c>
       <c r="H17" s="3">
-        <v>8459200</v>
+        <v>8586600</v>
       </c>
       <c r="I17" s="3">
-        <v>7848800</v>
+        <v>7967100</v>
       </c>
       <c r="J17" s="3">
-        <v>6438100</v>
+        <v>6535100</v>
       </c>
       <c r="K17" s="3">
         <v>7782500</v>
@@ -1092,25 +1092,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1121000</v>
+        <v>1137900</v>
       </c>
       <c r="E18" s="3">
-        <v>1107400</v>
+        <v>1124100</v>
       </c>
       <c r="F18" s="3">
-        <v>742400</v>
+        <v>753600</v>
       </c>
       <c r="G18" s="3">
-        <v>641200</v>
+        <v>650800</v>
       </c>
       <c r="H18" s="3">
-        <v>715900</v>
+        <v>726700</v>
       </c>
       <c r="I18" s="3">
-        <v>595600</v>
+        <v>604500</v>
       </c>
       <c r="J18" s="3">
-        <v>1385500</v>
+        <v>1406400</v>
       </c>
       <c r="K18" s="3">
         <v>686600</v>
@@ -1152,25 +1152,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>64500</v>
+        <v>65500</v>
       </c>
       <c r="E20" s="3">
-        <v>85200</v>
+        <v>86500</v>
       </c>
       <c r="F20" s="3">
-        <v>97600</v>
+        <v>99100</v>
       </c>
       <c r="G20" s="3">
-        <v>19800</v>
+        <v>20100</v>
       </c>
       <c r="H20" s="3">
-        <v>78900</v>
+        <v>80100</v>
       </c>
       <c r="I20" s="3">
-        <v>30400</v>
+        <v>30900</v>
       </c>
       <c r="J20" s="3">
-        <v>43100</v>
+        <v>43700</v>
       </c>
       <c r="K20" s="3">
         <v>11300</v>
@@ -1194,25 +1194,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2549100</v>
+        <v>2600000</v>
       </c>
       <c r="E21" s="3">
-        <v>2362700</v>
+        <v>2409000</v>
       </c>
       <c r="F21" s="3">
-        <v>1820700</v>
+        <v>1857100</v>
       </c>
       <c r="G21" s="3">
-        <v>1487100</v>
+        <v>1517100</v>
       </c>
       <c r="H21" s="3">
-        <v>1499700</v>
+        <v>1528700</v>
       </c>
       <c r="I21" s="3">
-        <v>1235200</v>
+        <v>1259400</v>
       </c>
       <c r="J21" s="3">
-        <v>2006900</v>
+        <v>2042400</v>
       </c>
       <c r="K21" s="3">
         <v>1303800</v>
@@ -1236,25 +1236,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>75200</v>
+        <v>76400</v>
       </c>
       <c r="E22" s="3">
-        <v>47200</v>
+        <v>47900</v>
       </c>
       <c r="F22" s="3">
-        <v>61400</v>
+        <v>62400</v>
       </c>
       <c r="G22" s="3">
-        <v>24400</v>
+        <v>24700</v>
       </c>
       <c r="H22" s="3">
-        <v>27600</v>
+        <v>28000</v>
       </c>
       <c r="I22" s="3">
-        <v>29600</v>
+        <v>30100</v>
       </c>
       <c r="J22" s="3">
-        <v>22800</v>
+        <v>23100</v>
       </c>
       <c r="K22" s="3">
         <v>22900</v>
@@ -1278,25 +1278,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1110300</v>
+        <v>1127100</v>
       </c>
       <c r="E23" s="3">
-        <v>1145300</v>
+        <v>1162600</v>
       </c>
       <c r="F23" s="3">
-        <v>778600</v>
+        <v>790400</v>
       </c>
       <c r="G23" s="3">
-        <v>636600</v>
+        <v>646200</v>
       </c>
       <c r="H23" s="3">
-        <v>767300</v>
+        <v>778800</v>
       </c>
       <c r="I23" s="3">
-        <v>596300</v>
+        <v>605300</v>
       </c>
       <c r="J23" s="3">
-        <v>1405800</v>
+        <v>1427000</v>
       </c>
       <c r="K23" s="3">
         <v>675000</v>
@@ -1320,25 +1320,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>351400</v>
+        <v>356700</v>
       </c>
       <c r="E24" s="3">
-        <v>270100</v>
+        <v>274100</v>
       </c>
       <c r="F24" s="3">
-        <v>283500</v>
+        <v>287800</v>
       </c>
       <c r="G24" s="3">
-        <v>257100</v>
+        <v>261000</v>
       </c>
       <c r="H24" s="3">
-        <v>219100</v>
+        <v>222400</v>
       </c>
       <c r="I24" s="3">
-        <v>171500</v>
+        <v>174100</v>
       </c>
       <c r="J24" s="3">
-        <v>439300</v>
+        <v>445900</v>
       </c>
       <c r="K24" s="3">
         <v>185300</v>
@@ -1404,25 +1404,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>759000</v>
+        <v>770400</v>
       </c>
       <c r="E26" s="3">
-        <v>875300</v>
+        <v>888400</v>
       </c>
       <c r="F26" s="3">
-        <v>495100</v>
+        <v>502500</v>
       </c>
       <c r="G26" s="3">
-        <v>379500</v>
+        <v>385200</v>
       </c>
       <c r="H26" s="3">
-        <v>548100</v>
+        <v>556400</v>
       </c>
       <c r="I26" s="3">
-        <v>424800</v>
+        <v>431200</v>
       </c>
       <c r="J26" s="3">
-        <v>966500</v>
+        <v>981100</v>
       </c>
       <c r="K26" s="3">
         <v>489700</v>
@@ -1446,25 +1446,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>758200</v>
+        <v>769600</v>
       </c>
       <c r="E27" s="3">
-        <v>871800</v>
+        <v>884900</v>
       </c>
       <c r="F27" s="3">
-        <v>496800</v>
+        <v>504300</v>
       </c>
       <c r="G27" s="3">
-        <v>383700</v>
+        <v>389400</v>
       </c>
       <c r="H27" s="3">
-        <v>545800</v>
+        <v>554100</v>
       </c>
       <c r="I27" s="3">
-        <v>421400</v>
+        <v>427700</v>
       </c>
       <c r="J27" s="3">
-        <v>963500</v>
+        <v>978000</v>
       </c>
       <c r="K27" s="3">
         <v>476500</v>
@@ -1545,7 +1545,7 @@
         <v>8</v>
       </c>
       <c r="I29" s="3">
-        <v>-23300</v>
+        <v>-23700</v>
       </c>
       <c r="J29" s="3" t="s">
         <v>8</v>
@@ -1656,25 +1656,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-64500</v>
+        <v>-65500</v>
       </c>
       <c r="E32" s="3">
-        <v>-85200</v>
+        <v>-86500</v>
       </c>
       <c r="F32" s="3">
-        <v>-97600</v>
+        <v>-99100</v>
       </c>
       <c r="G32" s="3">
-        <v>-19800</v>
+        <v>-20100</v>
       </c>
       <c r="H32" s="3">
-        <v>-78900</v>
+        <v>-80100</v>
       </c>
       <c r="I32" s="3">
-        <v>-30400</v>
+        <v>-30900</v>
       </c>
       <c r="J32" s="3">
-        <v>-43100</v>
+        <v>-43700</v>
       </c>
       <c r="K32" s="3">
         <v>-11300</v>
@@ -1698,25 +1698,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>758200</v>
+        <v>769600</v>
       </c>
       <c r="E33" s="3">
-        <v>871800</v>
+        <v>884900</v>
       </c>
       <c r="F33" s="3">
-        <v>496800</v>
+        <v>504300</v>
       </c>
       <c r="G33" s="3">
-        <v>383700</v>
+        <v>389400</v>
       </c>
       <c r="H33" s="3">
-        <v>545800</v>
+        <v>554100</v>
       </c>
       <c r="I33" s="3">
-        <v>398100</v>
+        <v>404100</v>
       </c>
       <c r="J33" s="3">
-        <v>963500</v>
+        <v>978000</v>
       </c>
       <c r="K33" s="3">
         <v>476500</v>
@@ -1782,25 +1782,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>758200</v>
+        <v>769600</v>
       </c>
       <c r="E35" s="3">
-        <v>871800</v>
+        <v>884900</v>
       </c>
       <c r="F35" s="3">
-        <v>496800</v>
+        <v>504300</v>
       </c>
       <c r="G35" s="3">
-        <v>383700</v>
+        <v>389400</v>
       </c>
       <c r="H35" s="3">
-        <v>545800</v>
+        <v>554100</v>
       </c>
       <c r="I35" s="3">
-        <v>398100</v>
+        <v>404100</v>
       </c>
       <c r="J35" s="3">
-        <v>963500</v>
+        <v>978000</v>
       </c>
       <c r="K35" s="3">
         <v>476500</v>
@@ -1907,25 +1907,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3361100</v>
+        <v>3411700</v>
       </c>
       <c r="E41" s="3">
-        <v>2917200</v>
+        <v>2961100</v>
       </c>
       <c r="F41" s="3">
-        <v>2525800</v>
+        <v>2563800</v>
       </c>
       <c r="G41" s="3">
-        <v>2209200</v>
+        <v>2242500</v>
       </c>
       <c r="H41" s="3">
-        <v>1920100</v>
+        <v>1949000</v>
       </c>
       <c r="I41" s="3">
-        <v>1856700</v>
+        <v>1884700</v>
       </c>
       <c r="J41" s="3">
-        <v>2193800</v>
+        <v>2226800</v>
       </c>
       <c r="K41" s="3">
         <v>2098200</v>
@@ -1949,25 +1949,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>346300</v>
+        <v>351500</v>
       </c>
       <c r="E42" s="3">
-        <v>444500</v>
+        <v>451200</v>
       </c>
       <c r="F42" s="3">
-        <v>939100</v>
+        <v>953300</v>
       </c>
       <c r="G42" s="3">
-        <v>216100</v>
+        <v>219400</v>
       </c>
       <c r="H42" s="3">
-        <v>269300</v>
+        <v>273400</v>
       </c>
       <c r="I42" s="3">
-        <v>289900</v>
+        <v>294300</v>
       </c>
       <c r="J42" s="3">
-        <v>372700</v>
+        <v>378300</v>
       </c>
       <c r="K42" s="3">
         <v>161400</v>
@@ -1991,25 +1991,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3820500</v>
+        <v>3878000</v>
       </c>
       <c r="E43" s="3">
-        <v>3687600</v>
+        <v>3743200</v>
       </c>
       <c r="F43" s="3">
-        <v>5960400</v>
+        <v>6050200</v>
       </c>
       <c r="G43" s="3">
-        <v>2120400</v>
+        <v>2152400</v>
       </c>
       <c r="H43" s="3">
-        <v>2091100</v>
+        <v>2122600</v>
       </c>
       <c r="I43" s="3">
-        <v>2059000</v>
+        <v>2090000</v>
       </c>
       <c r="J43" s="3">
-        <v>1733500</v>
+        <v>1759600</v>
       </c>
       <c r="K43" s="3">
         <v>1697000</v>
@@ -2033,25 +2033,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2941500</v>
+        <v>2985800</v>
       </c>
       <c r="E44" s="3">
-        <v>2901700</v>
+        <v>2945400</v>
       </c>
       <c r="F44" s="3">
-        <v>3832600</v>
+        <v>3890300</v>
       </c>
       <c r="G44" s="3">
-        <v>1570000</v>
+        <v>1593700</v>
       </c>
       <c r="H44" s="3">
-        <v>1506600</v>
+        <v>1529300</v>
       </c>
       <c r="I44" s="3">
-        <v>1378000</v>
+        <v>1398800</v>
       </c>
       <c r="J44" s="3">
-        <v>1025900</v>
+        <v>1041300</v>
       </c>
       <c r="K44" s="3">
         <v>1154900</v>
@@ -2075,25 +2075,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>203200</v>
+        <v>206300</v>
       </c>
       <c r="E45" s="3">
-        <v>229200</v>
+        <v>232700</v>
       </c>
       <c r="F45" s="3">
-        <v>579000</v>
+        <v>587700</v>
       </c>
       <c r="G45" s="3">
-        <v>301600</v>
+        <v>306100</v>
       </c>
       <c r="H45" s="3">
-        <v>338200</v>
+        <v>343200</v>
       </c>
       <c r="I45" s="3">
-        <v>392000</v>
+        <v>397900</v>
       </c>
       <c r="J45" s="3">
-        <v>425300</v>
+        <v>431700</v>
       </c>
       <c r="K45" s="3">
         <v>334800</v>
@@ -2117,25 +2117,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>10672500</v>
+        <v>10833300</v>
       </c>
       <c r="E46" s="3">
-        <v>10180300</v>
+        <v>10333600</v>
       </c>
       <c r="F46" s="3">
-        <v>8173000</v>
+        <v>8296100</v>
       </c>
       <c r="G46" s="3">
-        <v>6417400</v>
+        <v>6514100</v>
       </c>
       <c r="H46" s="3">
-        <v>6125300</v>
+        <v>6217500</v>
       </c>
       <c r="I46" s="3">
-        <v>5975600</v>
+        <v>6065600</v>
       </c>
       <c r="J46" s="3">
-        <v>5751100</v>
+        <v>5837800</v>
       </c>
       <c r="K46" s="3">
         <v>5446300</v>
@@ -2159,25 +2159,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1186300</v>
+        <v>1204100</v>
       </c>
       <c r="E47" s="3">
-        <v>931000</v>
+        <v>945100</v>
       </c>
       <c r="F47" s="3">
-        <v>679400</v>
+        <v>689600</v>
       </c>
       <c r="G47" s="3">
-        <v>220600</v>
+        <v>224000</v>
       </c>
       <c r="H47" s="3">
-        <v>1031200</v>
+        <v>1046800</v>
       </c>
       <c r="I47" s="3">
-        <v>1030800</v>
+        <v>1046300</v>
       </c>
       <c r="J47" s="3">
-        <v>1074500</v>
+        <v>1090700</v>
       </c>
       <c r="K47" s="3">
         <v>259700</v>
@@ -2201,25 +2201,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6540200</v>
+        <v>6638700</v>
       </c>
       <c r="E48" s="3">
-        <v>6608200</v>
+        <v>6707700</v>
       </c>
       <c r="F48" s="3">
-        <v>10948500</v>
+        <v>11113400</v>
       </c>
       <c r="G48" s="3">
-        <v>4318400</v>
+        <v>4383500</v>
       </c>
       <c r="H48" s="3">
-        <v>4004700</v>
+        <v>4065000</v>
       </c>
       <c r="I48" s="3">
-        <v>3623100</v>
+        <v>3677600</v>
       </c>
       <c r="J48" s="3">
-        <v>3085400</v>
+        <v>3131900</v>
       </c>
       <c r="K48" s="3">
         <v>3584100</v>
@@ -2243,25 +2243,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1399400</v>
+        <v>1420500</v>
       </c>
       <c r="E49" s="3">
-        <v>1370400</v>
+        <v>1391000</v>
       </c>
       <c r="F49" s="3">
-        <v>2904300</v>
+        <v>2948100</v>
       </c>
       <c r="G49" s="3">
-        <v>1598200</v>
+        <v>1622300</v>
       </c>
       <c r="H49" s="3">
-        <v>1683200</v>
+        <v>1708500</v>
       </c>
       <c r="I49" s="3">
-        <v>1616100</v>
+        <v>1640400</v>
       </c>
       <c r="J49" s="3">
-        <v>749300</v>
+        <v>760600</v>
       </c>
       <c r="K49" s="3">
         <v>873400</v>
@@ -2369,25 +2369,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1097800</v>
+        <v>1114300</v>
       </c>
       <c r="E52" s="3">
-        <v>1106700</v>
+        <v>1123400</v>
       </c>
       <c r="F52" s="3">
-        <v>446400</v>
+        <v>453100</v>
       </c>
       <c r="G52" s="3">
-        <v>349300</v>
+        <v>354600</v>
       </c>
       <c r="H52" s="3">
-        <v>385700</v>
+        <v>391500</v>
       </c>
       <c r="I52" s="3">
-        <v>405100</v>
+        <v>411200</v>
       </c>
       <c r="J52" s="3">
-        <v>390800</v>
+        <v>396700</v>
       </c>
       <c r="K52" s="3">
         <v>498200</v>
@@ -2453,25 +2453,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>20896300</v>
+        <v>21211000</v>
       </c>
       <c r="E54" s="3">
-        <v>20196600</v>
+        <v>20500700</v>
       </c>
       <c r="F54" s="3">
-        <v>15668200</v>
+        <v>15904100</v>
       </c>
       <c r="G54" s="3">
-        <v>12904000</v>
+        <v>13098400</v>
       </c>
       <c r="H54" s="3">
-        <v>13230100</v>
+        <v>13429300</v>
       </c>
       <c r="I54" s="3">
-        <v>12650600</v>
+        <v>12841100</v>
       </c>
       <c r="J54" s="3">
-        <v>11051200</v>
+        <v>11217600</v>
       </c>
       <c r="K54" s="3">
         <v>10661800</v>
@@ -2531,25 +2531,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2333600</v>
+        <v>2368700</v>
       </c>
       <c r="E57" s="3">
-        <v>3055300</v>
+        <v>3101300</v>
       </c>
       <c r="F57" s="3">
-        <v>4307700</v>
+        <v>4372500</v>
       </c>
       <c r="G57" s="3">
-        <v>1340100</v>
+        <v>1360300</v>
       </c>
       <c r="H57" s="3">
-        <v>1260900</v>
+        <v>1279900</v>
       </c>
       <c r="I57" s="3">
-        <v>1505900</v>
+        <v>1528600</v>
       </c>
       <c r="J57" s="3">
-        <v>1172900</v>
+        <v>1190600</v>
       </c>
       <c r="K57" s="3">
         <v>828100</v>
@@ -2573,25 +2573,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1718500</v>
+        <v>1744400</v>
       </c>
       <c r="E58" s="3">
-        <v>1230800</v>
+        <v>1249300</v>
       </c>
       <c r="F58" s="3">
-        <v>4413600</v>
+        <v>4480100</v>
       </c>
       <c r="G58" s="3">
-        <v>1889900</v>
+        <v>1918400</v>
       </c>
       <c r="H58" s="3">
-        <v>2075600</v>
+        <v>2106800</v>
       </c>
       <c r="I58" s="3">
-        <v>1255900</v>
+        <v>1274800</v>
       </c>
       <c r="J58" s="3">
-        <v>798100</v>
+        <v>810100</v>
       </c>
       <c r="K58" s="3">
         <v>1432600</v>
@@ -2615,25 +2615,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2616600</v>
+        <v>2656000</v>
       </c>
       <c r="E59" s="3">
-        <v>2768000</v>
+        <v>2809700</v>
       </c>
       <c r="F59" s="3">
-        <v>4823000</v>
+        <v>4895600</v>
       </c>
       <c r="G59" s="3">
-        <v>1543500</v>
+        <v>1566700</v>
       </c>
       <c r="H59" s="3">
-        <v>1406600</v>
+        <v>1427800</v>
       </c>
       <c r="I59" s="3">
-        <v>1242400</v>
+        <v>1261100</v>
       </c>
       <c r="J59" s="3">
-        <v>1200200</v>
+        <v>1218300</v>
       </c>
       <c r="K59" s="3">
         <v>1055900</v>
@@ -2657,25 +2657,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6668600</v>
+        <v>6769100</v>
       </c>
       <c r="E60" s="3">
-        <v>7054100</v>
+        <v>7160300</v>
       </c>
       <c r="F60" s="3">
-        <v>6828100</v>
+        <v>6930900</v>
       </c>
       <c r="G60" s="3">
-        <v>4773500</v>
+        <v>4845400</v>
       </c>
       <c r="H60" s="3">
-        <v>4743100</v>
+        <v>4814500</v>
       </c>
       <c r="I60" s="3">
-        <v>4004200</v>
+        <v>4064500</v>
       </c>
       <c r="J60" s="3">
-        <v>3171200</v>
+        <v>3219000</v>
       </c>
       <c r="K60" s="3">
         <v>3316600</v>
@@ -2699,25 +2699,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3275800</v>
+        <v>3325200</v>
       </c>
       <c r="E61" s="3">
-        <v>3283200</v>
+        <v>3332600</v>
       </c>
       <c r="F61" s="3">
-        <v>1229600</v>
+        <v>1248100</v>
       </c>
       <c r="G61" s="3">
-        <v>930000</v>
+        <v>944000</v>
       </c>
       <c r="H61" s="3">
-        <v>1379000</v>
+        <v>1399800</v>
       </c>
       <c r="I61" s="3">
-        <v>1951400</v>
+        <v>1980800</v>
       </c>
       <c r="J61" s="3">
-        <v>1420500</v>
+        <v>1441900</v>
       </c>
       <c r="K61" s="3">
         <v>1035200</v>
@@ -2741,25 +2741,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1238400</v>
+        <v>1257000</v>
       </c>
       <c r="E62" s="3">
-        <v>1202400</v>
+        <v>1220500</v>
       </c>
       <c r="F62" s="3">
-        <v>2198200</v>
+        <v>2231300</v>
       </c>
       <c r="G62" s="3">
-        <v>1566000</v>
+        <v>1589600</v>
       </c>
       <c r="H62" s="3">
-        <v>1239800</v>
+        <v>1258500</v>
       </c>
       <c r="I62" s="3">
-        <v>1175700</v>
+        <v>1193400</v>
       </c>
       <c r="J62" s="3">
-        <v>1133400</v>
+        <v>1150400</v>
       </c>
       <c r="K62" s="3">
         <v>1278000</v>
@@ -2909,25 +2909,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>11212200</v>
+        <v>11381000</v>
       </c>
       <c r="E66" s="3">
-        <v>11562500</v>
+        <v>11736600</v>
       </c>
       <c r="F66" s="3">
-        <v>9300900</v>
+        <v>9440900</v>
       </c>
       <c r="G66" s="3">
-        <v>7300200</v>
+        <v>7410100</v>
       </c>
       <c r="H66" s="3">
-        <v>7404900</v>
+        <v>7516400</v>
       </c>
       <c r="I66" s="3">
-        <v>7175000</v>
+        <v>7283100</v>
       </c>
       <c r="J66" s="3">
-        <v>5781600</v>
+        <v>5868600</v>
       </c>
       <c r="K66" s="3">
         <v>5697900</v>
@@ -3137,25 +3137,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>7003500</v>
+        <v>7108900</v>
       </c>
       <c r="E72" s="3">
-        <v>6472500</v>
+        <v>6569900</v>
       </c>
       <c r="F72" s="3">
-        <v>12467500</v>
+        <v>12655300</v>
       </c>
       <c r="G72" s="3">
-        <v>6748900</v>
+        <v>6850500</v>
       </c>
       <c r="H72" s="3">
-        <v>6507800</v>
+        <v>6605800</v>
       </c>
       <c r="I72" s="3">
-        <v>6108300</v>
+        <v>6200300</v>
       </c>
       <c r="J72" s="3">
-        <v>5787500</v>
+        <v>5874700</v>
       </c>
       <c r="K72" s="3">
         <v>5451700</v>
@@ -3305,25 +3305,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>9684100</v>
+        <v>9829900</v>
       </c>
       <c r="E76" s="3">
-        <v>8634100</v>
+        <v>8764100</v>
       </c>
       <c r="F76" s="3">
-        <v>6367300</v>
+        <v>6463200</v>
       </c>
       <c r="G76" s="3">
-        <v>5603900</v>
+        <v>5688300</v>
       </c>
       <c r="H76" s="3">
-        <v>5825200</v>
+        <v>5912900</v>
       </c>
       <c r="I76" s="3">
-        <v>5475600</v>
+        <v>5558000</v>
       </c>
       <c r="J76" s="3">
-        <v>5269600</v>
+        <v>5349000</v>
       </c>
       <c r="K76" s="3">
         <v>4963900</v>
@@ -3436,25 +3436,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>758200</v>
+        <v>769600</v>
       </c>
       <c r="E81" s="3">
-        <v>871800</v>
+        <v>884900</v>
       </c>
       <c r="F81" s="3">
-        <v>496800</v>
+        <v>504300</v>
       </c>
       <c r="G81" s="3">
-        <v>383700</v>
+        <v>389400</v>
       </c>
       <c r="H81" s="3">
-        <v>545800</v>
+        <v>554100</v>
       </c>
       <c r="I81" s="3">
-        <v>398100</v>
+        <v>404100</v>
       </c>
       <c r="J81" s="3">
-        <v>963500</v>
+        <v>978000</v>
       </c>
       <c r="K81" s="3">
         <v>476500</v>
@@ -3496,25 +3496,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1369700</v>
+        <v>1390400</v>
       </c>
       <c r="E83" s="3">
-        <v>1175500</v>
+        <v>1193200</v>
       </c>
       <c r="F83" s="3">
-        <v>985100</v>
+        <v>999900</v>
       </c>
       <c r="G83" s="3">
-        <v>829900</v>
+        <v>842400</v>
       </c>
       <c r="H83" s="3">
-        <v>708000</v>
+        <v>718700</v>
       </c>
       <c r="I83" s="3">
-        <v>612000</v>
+        <v>621200</v>
       </c>
       <c r="J83" s="3">
-        <v>580900</v>
+        <v>589700</v>
       </c>
       <c r="K83" s="3">
         <v>611700</v>
@@ -3748,25 +3748,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1744800</v>
+        <v>1771100</v>
       </c>
       <c r="E89" s="3">
-        <v>1188500</v>
+        <v>1206400</v>
       </c>
       <c r="F89" s="3">
-        <v>1532900</v>
+        <v>1556000</v>
       </c>
       <c r="G89" s="3">
-        <v>1476700</v>
+        <v>1498900</v>
       </c>
       <c r="H89" s="3">
-        <v>931400</v>
+        <v>945400</v>
       </c>
       <c r="I89" s="3">
-        <v>606300</v>
+        <v>615400</v>
       </c>
       <c r="J89" s="3">
-        <v>1063300</v>
+        <v>1079300</v>
       </c>
       <c r="K89" s="3">
         <v>1114000</v>
@@ -3808,25 +3808,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1830700</v>
+        <v>-1858300</v>
       </c>
       <c r="E91" s="3">
-        <v>-1934500</v>
+        <v>-1963600</v>
       </c>
       <c r="F91" s="3">
-        <v>-1409000</v>
+        <v>-1430200</v>
       </c>
       <c r="G91" s="3">
-        <v>-1151600</v>
+        <v>-1168900</v>
       </c>
       <c r="H91" s="3">
-        <v>-1152700</v>
+        <v>-1170000</v>
       </c>
       <c r="I91" s="3">
-        <v>-1186000</v>
+        <v>-1203800</v>
       </c>
       <c r="J91" s="3">
-        <v>-1113100</v>
+        <v>-1129800</v>
       </c>
       <c r="K91" s="3">
         <v>-1181000</v>
@@ -3934,25 +3934,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1556400</v>
+        <v>-1579900</v>
       </c>
       <c r="E94" s="3">
-        <v>-1869500</v>
+        <v>-1897600</v>
       </c>
       <c r="F94" s="3">
-        <v>-1536600</v>
+        <v>-1559800</v>
       </c>
       <c r="G94" s="3">
-        <v>-278600</v>
+        <v>-282800</v>
       </c>
       <c r="H94" s="3">
-        <v>-930800</v>
+        <v>-944800</v>
       </c>
       <c r="I94" s="3">
-        <v>-1634100</v>
+        <v>-1658700</v>
       </c>
       <c r="J94" s="3">
-        <v>-472200</v>
+        <v>-479300</v>
       </c>
       <c r="K94" s="3">
         <v>-1033300</v>
@@ -3994,25 +3994,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-247000</v>
+        <v>-250700</v>
       </c>
       <c r="E96" s="3">
-        <v>-159300</v>
+        <v>-161700</v>
       </c>
       <c r="F96" s="3">
-        <v>-151000</v>
+        <v>-153300</v>
       </c>
       <c r="G96" s="3">
-        <v>-142600</v>
+        <v>-144700</v>
       </c>
       <c r="H96" s="3">
-        <v>-125800</v>
+        <v>-127700</v>
       </c>
       <c r="I96" s="3">
-        <v>-100500</v>
+        <v>-102000</v>
       </c>
       <c r="J96" s="3">
-        <v>-100500</v>
+        <v>-102000</v>
       </c>
       <c r="K96" s="3">
         <v>-101900</v>
@@ -4162,25 +4162,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>99200</v>
+        <v>100700</v>
       </c>
       <c r="E100" s="3">
-        <v>755300</v>
+        <v>766600</v>
       </c>
       <c r="F100" s="3">
-        <v>140000</v>
+        <v>142100</v>
       </c>
       <c r="G100" s="3">
-        <v>-808500</v>
+        <v>-820700</v>
       </c>
       <c r="H100" s="3">
-        <v>62600</v>
+        <v>63600</v>
       </c>
       <c r="I100" s="3">
-        <v>731000</v>
+        <v>742000</v>
       </c>
       <c r="J100" s="3">
-        <v>-250700</v>
+        <v>-254500</v>
       </c>
       <c r="K100" s="3">
         <v>215400</v>
@@ -4204,25 +4204,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>156200</v>
+        <v>158600</v>
       </c>
       <c r="E101" s="3">
-        <v>317200</v>
+        <v>322000</v>
       </c>
       <c r="F101" s="3">
-        <v>180300</v>
+        <v>183000</v>
       </c>
       <c r="G101" s="3">
-        <v>-100400</v>
+        <v>-101900</v>
       </c>
       <c r="H101" s="3">
         <v>100</v>
       </c>
       <c r="I101" s="3">
-        <v>-40300</v>
+        <v>-40900</v>
       </c>
       <c r="J101" s="3">
-        <v>-42200</v>
+        <v>-42800</v>
       </c>
       <c r="K101" s="3">
         <v>-146400</v>
@@ -4246,25 +4246,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>443900</v>
+        <v>450500</v>
       </c>
       <c r="E102" s="3">
-        <v>391400</v>
+        <v>397300</v>
       </c>
       <c r="F102" s="3">
-        <v>316500</v>
+        <v>321300</v>
       </c>
       <c r="G102" s="3">
-        <v>289100</v>
+        <v>293500</v>
       </c>
       <c r="H102" s="3">
-        <v>63400</v>
+        <v>64400</v>
       </c>
       <c r="I102" s="3">
-        <v>-337100</v>
+        <v>-342100</v>
       </c>
       <c r="J102" s="3">
-        <v>298300</v>
+        <v>302800</v>
       </c>
       <c r="K102" s="3">
         <v>149700</v>

--- a/AAII_Financials/Yearly/TTDKY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TTDKY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
   <si>
     <t>TTDKY</t>
   </si>
@@ -656,195 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45016</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44651</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44286</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43921</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43555</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43190</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42825</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42460</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42094</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41729</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41364</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40999</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>14698700</v>
+        <v>13422700</v>
       </c>
       <c r="E8" s="3">
-        <v>12820300</v>
+        <v>13913600</v>
       </c>
       <c r="F8" s="3">
-        <v>9968500</v>
+        <v>12135600</v>
       </c>
       <c r="G8" s="3">
-        <v>9186900</v>
+        <v>9436100</v>
       </c>
       <c r="H8" s="3">
-        <v>9313400</v>
+        <v>8696200</v>
       </c>
       <c r="I8" s="3">
-        <v>8571600</v>
+        <v>8815900</v>
       </c>
       <c r="J8" s="3">
+        <v>8113700</v>
+      </c>
+      <c r="K8" s="3">
         <v>7941500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8469100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9234200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9018200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>7740800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7363100</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>10759000</v>
+        <v>9575500</v>
       </c>
       <c r="E9" s="3">
-        <v>9020000</v>
+        <v>10184400</v>
       </c>
       <c r="F9" s="3">
-        <v>7093200</v>
+        <v>8538200</v>
       </c>
       <c r="G9" s="3">
-        <v>6468500</v>
+        <v>6714400</v>
       </c>
       <c r="H9" s="3">
-        <v>6641100</v>
+        <v>6123000</v>
       </c>
       <c r="I9" s="3">
-        <v>6258300</v>
+        <v>6286300</v>
       </c>
       <c r="J9" s="3">
+        <v>5924000</v>
+      </c>
+      <c r="K9" s="3">
         <v>5769100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>6108800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6843000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6994300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6145600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5733700</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3939700</v>
+        <v>3847300</v>
       </c>
       <c r="E10" s="3">
-        <v>3800300</v>
+        <v>3729300</v>
       </c>
       <c r="F10" s="3">
-        <v>2875300</v>
+        <v>3597400</v>
       </c>
       <c r="G10" s="3">
-        <v>2718400</v>
+        <v>2721700</v>
       </c>
       <c r="H10" s="3">
-        <v>2672300</v>
+        <v>2573200</v>
       </c>
       <c r="I10" s="3">
-        <v>2313300</v>
+        <v>2529600</v>
       </c>
       <c r="J10" s="3">
+        <v>2189800</v>
+      </c>
+      <c r="K10" s="3">
         <v>2172400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2360300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2391300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2023900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1595300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1629400</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -861,8 +873,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -902,9 +915,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -944,26 +960,29 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>-12100</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E14" s="3">
-        <v>-50400</v>
+        <v>-9700</v>
       </c>
       <c r="F14" s="3">
-        <v>10000</v>
+        <v>-44300</v>
       </c>
       <c r="G14" s="3">
-        <v>134100</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+        <v>11100</v>
+      </c>
+      <c r="H14" s="3">
+        <v>126900</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -980,15 +999,18 @@
       <c r="M14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-60900</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1028,9 +1050,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1044,92 +1069,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13560800</v>
+        <v>12319700</v>
       </c>
       <c r="E17" s="3">
-        <v>11696300</v>
+        <v>12836500</v>
       </c>
       <c r="F17" s="3">
-        <v>9214900</v>
+        <v>11071500</v>
       </c>
       <c r="G17" s="3">
-        <v>8536000</v>
+        <v>8722700</v>
       </c>
       <c r="H17" s="3">
-        <v>8586600</v>
+        <v>8080100</v>
       </c>
       <c r="I17" s="3">
-        <v>7967100</v>
+        <v>8128000</v>
       </c>
       <c r="J17" s="3">
+        <v>7541500</v>
+      </c>
+      <c r="K17" s="3">
         <v>6535100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>7782500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>8616200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8682800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>7544000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7194100</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1137900</v>
+        <v>1103100</v>
       </c>
       <c r="E18" s="3">
-        <v>1124100</v>
+        <v>1077100</v>
       </c>
       <c r="F18" s="3">
-        <v>753600</v>
+        <v>1064000</v>
       </c>
       <c r="G18" s="3">
-        <v>650800</v>
+        <v>713400</v>
       </c>
       <c r="H18" s="3">
-        <v>726700</v>
+        <v>616100</v>
       </c>
       <c r="I18" s="3">
-        <v>604500</v>
+        <v>687900</v>
       </c>
       <c r="J18" s="3">
+        <v>572200</v>
+      </c>
+      <c r="K18" s="3">
         <v>1406400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>686600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>618100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>335400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>196800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>168900</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1146,218 +1178,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>65500</v>
+        <v>40500</v>
       </c>
       <c r="E20" s="3">
-        <v>86500</v>
+        <v>62000</v>
       </c>
       <c r="F20" s="3">
-        <v>99100</v>
+        <v>81800</v>
       </c>
       <c r="G20" s="3">
-        <v>20100</v>
+        <v>93800</v>
       </c>
       <c r="H20" s="3">
-        <v>80100</v>
+        <v>19000</v>
       </c>
       <c r="I20" s="3">
-        <v>30900</v>
+        <v>75800</v>
       </c>
       <c r="J20" s="3">
+        <v>29200</v>
+      </c>
+      <c r="K20" s="3">
         <v>43700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>11300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>43100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>60600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-31300</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2600000</v>
+        <v>2357300</v>
       </c>
       <c r="E21" s="3">
-        <v>2409000</v>
+        <v>2453200</v>
       </c>
       <c r="F21" s="3">
-        <v>1857100</v>
+        <v>2273600</v>
       </c>
       <c r="G21" s="3">
-        <v>1517100</v>
+        <v>1752200</v>
       </c>
       <c r="H21" s="3">
-        <v>1528700</v>
+        <v>1431300</v>
       </c>
       <c r="I21" s="3">
-        <v>1259400</v>
+        <v>1443000</v>
       </c>
       <c r="J21" s="3">
+        <v>1188600</v>
+      </c>
+      <c r="K21" s="3">
         <v>2042400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1303800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1353700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1160600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>907300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>863400</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>76400</v>
+      <c r="D22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E22" s="3">
-        <v>47900</v>
+        <v>72300</v>
       </c>
       <c r="F22" s="3">
-        <v>62400</v>
+        <v>45400</v>
       </c>
       <c r="G22" s="3">
-        <v>24700</v>
+        <v>59000</v>
       </c>
       <c r="H22" s="3">
-        <v>28000</v>
+        <v>23400</v>
       </c>
       <c r="I22" s="3">
-        <v>30100</v>
+        <v>26500</v>
       </c>
       <c r="J22" s="3">
+        <v>28500</v>
+      </c>
+      <c r="K22" s="3">
         <v>23100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>22900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>25500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>31700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>25800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>26900</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1127100</v>
+        <v>1143600</v>
       </c>
       <c r="E23" s="3">
-        <v>1162600</v>
+        <v>1066900</v>
       </c>
       <c r="F23" s="3">
-        <v>790400</v>
+        <v>1100500</v>
       </c>
       <c r="G23" s="3">
-        <v>646200</v>
+        <v>748100</v>
       </c>
       <c r="H23" s="3">
-        <v>778800</v>
+        <v>611700</v>
       </c>
       <c r="I23" s="3">
-        <v>605300</v>
+        <v>737200</v>
       </c>
       <c r="J23" s="3">
+        <v>573000</v>
+      </c>
+      <c r="K23" s="3">
         <v>1427000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>675000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>635600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>364300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>171400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>110700</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>356700</v>
+        <v>338800</v>
       </c>
       <c r="E24" s="3">
-        <v>274100</v>
+        <v>337600</v>
       </c>
       <c r="F24" s="3">
-        <v>287800</v>
+        <v>259500</v>
       </c>
       <c r="G24" s="3">
-        <v>261000</v>
+        <v>272400</v>
       </c>
       <c r="H24" s="3">
-        <v>222400</v>
+        <v>247000</v>
       </c>
       <c r="I24" s="3">
-        <v>174100</v>
+        <v>210600</v>
       </c>
       <c r="J24" s="3">
+        <v>164800</v>
+      </c>
+      <c r="K24" s="3">
         <v>445900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>185300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>185400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>164300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>130200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>103800</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1397,93 +1445,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>770400</v>
+        <v>804700</v>
       </c>
       <c r="E26" s="3">
-        <v>888400</v>
+        <v>729200</v>
       </c>
       <c r="F26" s="3">
-        <v>502500</v>
+        <v>841000</v>
       </c>
       <c r="G26" s="3">
-        <v>385200</v>
+        <v>475700</v>
       </c>
       <c r="H26" s="3">
-        <v>556400</v>
+        <v>364700</v>
       </c>
       <c r="I26" s="3">
-        <v>431200</v>
+        <v>526700</v>
       </c>
       <c r="J26" s="3">
+        <v>408200</v>
+      </c>
+      <c r="K26" s="3">
         <v>981100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>489700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>450200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>200000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>41200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>6900</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>769600</v>
+        <v>795500</v>
       </c>
       <c r="E27" s="3">
-        <v>884900</v>
+        <v>728500</v>
       </c>
       <c r="F27" s="3">
-        <v>504300</v>
+        <v>837700</v>
       </c>
       <c r="G27" s="3">
-        <v>389400</v>
+        <v>477300</v>
       </c>
       <c r="H27" s="3">
-        <v>554100</v>
+        <v>368600</v>
       </c>
       <c r="I27" s="3">
-        <v>427700</v>
+        <v>524500</v>
       </c>
       <c r="J27" s="3">
+        <v>404900</v>
+      </c>
+      <c r="K27" s="3">
         <v>978000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>476500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>421700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>182200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>10900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-5800</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1523,9 +1580,12 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1544,11 +1604,11 @@
       <c r="H29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I29" s="3">
-        <v>-23700</v>
-      </c>
-      <c r="J29" s="3" t="s">
+      <c r="I29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="J29" s="3">
+        <v>-22400</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1556,18 +1616,21 @@
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
+      <c r="M29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N29" s="3">
         <v>-33000</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>-16400</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1607,9 +1670,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1649,93 +1715,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-65500</v>
+        <v>-40500</v>
       </c>
       <c r="E32" s="3">
-        <v>-86500</v>
+        <v>-62000</v>
       </c>
       <c r="F32" s="3">
-        <v>-99100</v>
+        <v>-81800</v>
       </c>
       <c r="G32" s="3">
-        <v>-20100</v>
+        <v>-93800</v>
       </c>
       <c r="H32" s="3">
-        <v>-80100</v>
+        <v>-19000</v>
       </c>
       <c r="I32" s="3">
-        <v>-30900</v>
+        <v>-75800</v>
       </c>
       <c r="J32" s="3">
+        <v>-29200</v>
+      </c>
+      <c r="K32" s="3">
         <v>-43700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-11300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-43100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-60600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>31300</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>769600</v>
+        <v>795500</v>
       </c>
       <c r="E33" s="3">
-        <v>884900</v>
+        <v>728500</v>
       </c>
       <c r="F33" s="3">
-        <v>504300</v>
+        <v>837700</v>
       </c>
       <c r="G33" s="3">
-        <v>389400</v>
+        <v>477300</v>
       </c>
       <c r="H33" s="3">
-        <v>554100</v>
+        <v>368600</v>
       </c>
       <c r="I33" s="3">
-        <v>404100</v>
+        <v>524500</v>
       </c>
       <c r="J33" s="3">
+        <v>382500</v>
+      </c>
+      <c r="K33" s="3">
         <v>978000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>476500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>421700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>149200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>10900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-22200</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1775,98 +1850,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>769600</v>
+        <v>795500</v>
       </c>
       <c r="E35" s="3">
-        <v>884900</v>
+        <v>728500</v>
       </c>
       <c r="F35" s="3">
-        <v>504300</v>
+        <v>837700</v>
       </c>
       <c r="G35" s="3">
-        <v>389400</v>
+        <v>477300</v>
       </c>
       <c r="H35" s="3">
-        <v>554100</v>
+        <v>368600</v>
       </c>
       <c r="I35" s="3">
-        <v>404100</v>
+        <v>524500</v>
       </c>
       <c r="J35" s="3">
+        <v>382500</v>
+      </c>
+      <c r="K35" s="3">
         <v>978000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>476500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>421700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>149200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>10900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-22200</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45016</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44651</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44286</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43921</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43555</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43190</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42825</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42460</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42094</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41729</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41364</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40999</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1883,8 +1967,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1901,386 +1986,414 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>3411700</v>
+        <v>4147000</v>
       </c>
       <c r="E41" s="3">
-        <v>2961100</v>
+        <v>3229500</v>
       </c>
       <c r="F41" s="3">
-        <v>2563800</v>
+        <v>2803000</v>
       </c>
       <c r="G41" s="3">
-        <v>2242500</v>
+        <v>2426900</v>
       </c>
       <c r="H41" s="3">
-        <v>1949000</v>
+        <v>2122700</v>
       </c>
       <c r="I41" s="3">
-        <v>1884700</v>
+        <v>1844900</v>
       </c>
       <c r="J41" s="3">
+        <v>1784000</v>
+      </c>
+      <c r="K41" s="3">
         <v>2226800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2098200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2261300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2297800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1942400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1509800</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>351500</v>
+        <v>300200</v>
       </c>
       <c r="E42" s="3">
-        <v>451200</v>
+        <v>332700</v>
       </c>
       <c r="F42" s="3">
-        <v>953300</v>
+        <v>427100</v>
       </c>
       <c r="G42" s="3">
-        <v>219400</v>
+        <v>902400</v>
       </c>
       <c r="H42" s="3">
-        <v>273400</v>
+        <v>207700</v>
       </c>
       <c r="I42" s="3">
-        <v>294300</v>
+        <v>258800</v>
       </c>
       <c r="J42" s="3">
+        <v>278600</v>
+      </c>
+      <c r="K42" s="3">
         <v>378300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>161400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>182500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>79600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>97500</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>65000</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3878000</v>
+        <v>3592700</v>
       </c>
       <c r="E43" s="3">
-        <v>3743200</v>
+        <v>3670900</v>
       </c>
       <c r="F43" s="3">
-        <v>6050200</v>
+        <v>3543200</v>
       </c>
       <c r="G43" s="3">
-        <v>2152400</v>
+        <v>5727000</v>
       </c>
       <c r="H43" s="3">
-        <v>2122600</v>
+        <v>2037400</v>
       </c>
       <c r="I43" s="3">
-        <v>2090000</v>
+        <v>2009200</v>
       </c>
       <c r="J43" s="3">
+        <v>1978300</v>
+      </c>
+      <c r="K43" s="3">
         <v>1759600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1697000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2071600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1939900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1773000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1655000</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2985800</v>
+        <v>2590800</v>
       </c>
       <c r="E44" s="3">
-        <v>2945400</v>
+        <v>2826300</v>
       </c>
       <c r="F44" s="3">
-        <v>3890300</v>
+        <v>2788100</v>
       </c>
       <c r="G44" s="3">
-        <v>1593700</v>
+        <v>3682500</v>
       </c>
       <c r="H44" s="3">
-        <v>1529300</v>
+        <v>1508600</v>
       </c>
       <c r="I44" s="3">
-        <v>1398800</v>
+        <v>1447600</v>
       </c>
       <c r="J44" s="3">
+        <v>1324100</v>
+      </c>
+      <c r="K44" s="3">
         <v>1041300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1154900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1288100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1249300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1253200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1240600</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>206300</v>
+        <v>393700</v>
       </c>
       <c r="E45" s="3">
-        <v>232700</v>
+        <v>195200</v>
       </c>
       <c r="F45" s="3">
-        <v>587700</v>
+        <v>220200</v>
       </c>
       <c r="G45" s="3">
-        <v>306100</v>
+        <v>556300</v>
       </c>
       <c r="H45" s="3">
-        <v>343200</v>
+        <v>289800</v>
       </c>
       <c r="I45" s="3">
-        <v>397900</v>
+        <v>324900</v>
       </c>
       <c r="J45" s="3">
+        <v>376600</v>
+      </c>
+      <c r="K45" s="3">
         <v>431700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>334800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>510800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>417500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>484400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>463800</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>10833300</v>
+        <v>11024500</v>
       </c>
       <c r="E46" s="3">
-        <v>10333600</v>
+        <v>10254600</v>
       </c>
       <c r="F46" s="3">
-        <v>8296100</v>
+        <v>9781600</v>
       </c>
       <c r="G46" s="3">
-        <v>6514100</v>
+        <v>7853000</v>
       </c>
       <c r="H46" s="3">
-        <v>6217500</v>
+        <v>6166200</v>
       </c>
       <c r="I46" s="3">
-        <v>6065600</v>
+        <v>5885500</v>
       </c>
       <c r="J46" s="3">
+        <v>5741600</v>
+      </c>
+      <c r="K46" s="3">
         <v>5837800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5446300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6314300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5984100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5550600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4934200</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1204100</v>
+        <v>1412600</v>
       </c>
       <c r="E47" s="3">
-        <v>945100</v>
+        <v>1139800</v>
       </c>
       <c r="F47" s="3">
-        <v>689600</v>
+        <v>894600</v>
       </c>
       <c r="G47" s="3">
-        <v>224000</v>
+        <v>652800</v>
       </c>
       <c r="H47" s="3">
-        <v>1046800</v>
+        <v>212000</v>
       </c>
       <c r="I47" s="3">
-        <v>1046300</v>
+        <v>990900</v>
       </c>
       <c r="J47" s="3">
+        <v>990400</v>
+      </c>
+      <c r="K47" s="3">
         <v>1090700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>259700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>390100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>351800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>292800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>320500</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6638700</v>
+        <v>6778200</v>
       </c>
       <c r="E48" s="3">
-        <v>6707700</v>
+        <v>6284100</v>
       </c>
       <c r="F48" s="3">
-        <v>11113400</v>
+        <v>6349400</v>
       </c>
       <c r="G48" s="3">
-        <v>4383500</v>
+        <v>10519800</v>
       </c>
       <c r="H48" s="3">
-        <v>4065000</v>
+        <v>4149300</v>
       </c>
       <c r="I48" s="3">
-        <v>3677600</v>
+        <v>3847800</v>
       </c>
       <c r="J48" s="3">
+        <v>3481200</v>
+      </c>
+      <c r="K48" s="3">
         <v>3131900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3584100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3644500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3426100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3326000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3004200</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1420500</v>
+        <v>1438700</v>
       </c>
       <c r="E49" s="3">
-        <v>1391000</v>
+        <v>1344600</v>
       </c>
       <c r="F49" s="3">
-        <v>2948100</v>
+        <v>1316700</v>
       </c>
       <c r="G49" s="3">
-        <v>1622300</v>
+        <v>2790600</v>
       </c>
       <c r="H49" s="3">
-        <v>1708500</v>
+        <v>1535600</v>
       </c>
       <c r="I49" s="3">
-        <v>1640400</v>
+        <v>1617200</v>
       </c>
       <c r="J49" s="3">
+        <v>1552800</v>
+      </c>
+      <c r="K49" s="3">
         <v>760600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>873400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>946900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1081800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1036600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>981500</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2320,9 +2433,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2362,51 +2478,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1114300</v>
+        <v>1135700</v>
       </c>
       <c r="E52" s="3">
-        <v>1123400</v>
+        <v>1054800</v>
       </c>
       <c r="F52" s="3">
-        <v>453100</v>
+        <v>1063400</v>
       </c>
       <c r="G52" s="3">
-        <v>354600</v>
+        <v>428900</v>
       </c>
       <c r="H52" s="3">
-        <v>391500</v>
+        <v>335700</v>
       </c>
       <c r="I52" s="3">
-        <v>411200</v>
+        <v>370600</v>
       </c>
       <c r="J52" s="3">
+        <v>389200</v>
+      </c>
+      <c r="K52" s="3">
         <v>396700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>498200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>682800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>510800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>425900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>457900</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2446,51 +2568,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>21211000</v>
+        <v>21789600</v>
       </c>
       <c r="E54" s="3">
-        <v>20500700</v>
+        <v>20078000</v>
       </c>
       <c r="F54" s="3">
-        <v>15904100</v>
+        <v>19405700</v>
       </c>
       <c r="G54" s="3">
-        <v>13098400</v>
+        <v>15054600</v>
       </c>
       <c r="H54" s="3">
-        <v>13429300</v>
+        <v>12398800</v>
       </c>
       <c r="I54" s="3">
-        <v>12841100</v>
+        <v>12712000</v>
       </c>
       <c r="J54" s="3">
+        <v>12155200</v>
+      </c>
+      <c r="K54" s="3">
         <v>11217600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10661800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11978500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11354600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10632000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9698400</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2507,8 +2635,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2525,260 +2654,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2368700</v>
+        <v>2245400</v>
       </c>
       <c r="E57" s="3">
-        <v>3101300</v>
+        <v>2242200</v>
       </c>
       <c r="F57" s="3">
-        <v>4372500</v>
+        <v>2935600</v>
       </c>
       <c r="G57" s="3">
-        <v>1360300</v>
+        <v>4139000</v>
       </c>
       <c r="H57" s="3">
-        <v>1279900</v>
+        <v>1287600</v>
       </c>
       <c r="I57" s="3">
-        <v>1528600</v>
+        <v>1211500</v>
       </c>
       <c r="J57" s="3">
+        <v>1446900</v>
+      </c>
+      <c r="K57" s="3">
         <v>1190600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>828100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>951900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>876500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>772800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>792500</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1744400</v>
+        <v>1432500</v>
       </c>
       <c r="E58" s="3">
-        <v>1249300</v>
+        <v>1651200</v>
       </c>
       <c r="F58" s="3">
-        <v>4480100</v>
+        <v>1182600</v>
       </c>
       <c r="G58" s="3">
-        <v>1918400</v>
+        <v>4240800</v>
       </c>
       <c r="H58" s="3">
-        <v>2106800</v>
+        <v>1815900</v>
       </c>
       <c r="I58" s="3">
-        <v>1274800</v>
+        <v>1994300</v>
       </c>
       <c r="J58" s="3">
+        <v>1206700</v>
+      </c>
+      <c r="K58" s="3">
         <v>810100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1432600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1167300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1551600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1801100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1291800</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2656000</v>
+        <v>2809900</v>
       </c>
       <c r="E59" s="3">
-        <v>2809700</v>
+        <v>2514100</v>
       </c>
       <c r="F59" s="3">
-        <v>4895600</v>
+        <v>2659600</v>
       </c>
       <c r="G59" s="3">
-        <v>1566700</v>
+        <v>4634100</v>
       </c>
       <c r="H59" s="3">
-        <v>1427800</v>
+        <v>1483000</v>
       </c>
       <c r="I59" s="3">
-        <v>1261100</v>
+        <v>1351600</v>
       </c>
       <c r="J59" s="3">
+        <v>1193700</v>
+      </c>
+      <c r="K59" s="3">
         <v>1218300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1055900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1189400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>995800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>861600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>861900</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6769100</v>
+        <v>6487800</v>
       </c>
       <c r="E60" s="3">
-        <v>7160300</v>
+        <v>6407500</v>
       </c>
       <c r="F60" s="3">
-        <v>6930900</v>
+        <v>6777800</v>
       </c>
       <c r="G60" s="3">
-        <v>4845400</v>
+        <v>6560700</v>
       </c>
       <c r="H60" s="3">
-        <v>4814500</v>
+        <v>4586600</v>
       </c>
       <c r="I60" s="3">
-        <v>4064500</v>
+        <v>4557400</v>
       </c>
       <c r="J60" s="3">
+        <v>3847400</v>
+      </c>
+      <c r="K60" s="3">
         <v>3219000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3316600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3308600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3423800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3435400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2946200</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3325200</v>
+        <v>2942500</v>
       </c>
       <c r="E61" s="3">
-        <v>3332600</v>
+        <v>3147600</v>
       </c>
       <c r="F61" s="3">
-        <v>1248100</v>
+        <v>3154600</v>
       </c>
       <c r="G61" s="3">
-        <v>944000</v>
+        <v>1181500</v>
       </c>
       <c r="H61" s="3">
-        <v>1399800</v>
+        <v>893600</v>
       </c>
       <c r="I61" s="3">
-        <v>1980800</v>
+        <v>1325000</v>
       </c>
       <c r="J61" s="3">
+        <v>1875000</v>
+      </c>
+      <c r="K61" s="3">
         <v>1441900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1035200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1121500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>894200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>886100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1174700</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1257000</v>
+        <v>1418100</v>
       </c>
       <c r="E62" s="3">
-        <v>1220500</v>
+        <v>1189900</v>
       </c>
       <c r="F62" s="3">
-        <v>2231300</v>
+        <v>1155300</v>
       </c>
       <c r="G62" s="3">
-        <v>1589600</v>
+        <v>2112100</v>
       </c>
       <c r="H62" s="3">
-        <v>1258500</v>
+        <v>1504700</v>
       </c>
       <c r="I62" s="3">
-        <v>1193400</v>
+        <v>1191300</v>
       </c>
       <c r="J62" s="3">
+        <v>1129600</v>
+      </c>
+      <c r="K62" s="3">
         <v>1150400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1278000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1082600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1062000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1032700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>948600</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2818,9 +2966,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2860,9 +3011,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2902,51 +3056,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>11381000</v>
+        <v>10896900</v>
       </c>
       <c r="E66" s="3">
-        <v>11736600</v>
+        <v>10773100</v>
       </c>
       <c r="F66" s="3">
-        <v>9440900</v>
+        <v>11109700</v>
       </c>
       <c r="G66" s="3">
-        <v>7410100</v>
+        <v>8936700</v>
       </c>
       <c r="H66" s="3">
-        <v>7516400</v>
+        <v>7014300</v>
       </c>
       <c r="I66" s="3">
-        <v>7283100</v>
+        <v>7114900</v>
       </c>
       <c r="J66" s="3">
+        <v>6894100</v>
+      </c>
+      <c r="K66" s="3">
         <v>5868600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5697900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5676000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5535000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5531000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5195000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2963,8 +3123,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3004,9 +3165,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3046,9 +3210,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3088,9 +3255,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3130,51 +3300,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>7108900</v>
+        <v>7265100</v>
       </c>
       <c r="E72" s="3">
-        <v>6569900</v>
+        <v>6729200</v>
       </c>
       <c r="F72" s="3">
-        <v>12655300</v>
+        <v>6219000</v>
       </c>
       <c r="G72" s="3">
-        <v>6850500</v>
+        <v>11979300</v>
       </c>
       <c r="H72" s="3">
-        <v>6605800</v>
+        <v>6484600</v>
       </c>
       <c r="I72" s="3">
-        <v>6200300</v>
+        <v>6252900</v>
       </c>
       <c r="J72" s="3">
+        <v>5869100</v>
+      </c>
+      <c r="K72" s="3">
         <v>5874700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5451700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5892900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5968400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5843100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5891000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3214,9 +3390,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3256,9 +3435,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3298,51 +3480,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>9829900</v>
+        <v>10892800</v>
       </c>
       <c r="E76" s="3">
-        <v>8764100</v>
+        <v>9304900</v>
       </c>
       <c r="F76" s="3">
-        <v>6463200</v>
+        <v>8296000</v>
       </c>
       <c r="G76" s="3">
-        <v>5688300</v>
+        <v>6118000</v>
       </c>
       <c r="H76" s="3">
-        <v>5912900</v>
+        <v>5384400</v>
       </c>
       <c r="I76" s="3">
-        <v>5558000</v>
+        <v>5597100</v>
       </c>
       <c r="J76" s="3">
+        <v>5261200</v>
+      </c>
+      <c r="K76" s="3">
         <v>5349000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4963900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>6302500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5819600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5101000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4503400</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3382,98 +3570,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45016</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44651</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44286</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43921</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43555</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43190</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42825</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42460</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42094</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41729</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41364</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40999</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>769600</v>
+        <v>795500</v>
       </c>
       <c r="E81" s="3">
-        <v>884900</v>
+        <v>728500</v>
       </c>
       <c r="F81" s="3">
-        <v>504300</v>
+        <v>837700</v>
       </c>
       <c r="G81" s="3">
-        <v>389400</v>
+        <v>477300</v>
       </c>
       <c r="H81" s="3">
-        <v>554100</v>
+        <v>368600</v>
       </c>
       <c r="I81" s="3">
-        <v>404100</v>
+        <v>524500</v>
       </c>
       <c r="J81" s="3">
+        <v>382500</v>
+      </c>
+      <c r="K81" s="3">
         <v>978000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>476500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>421700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>149200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>10900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-22200</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3490,50 +3687,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1390400</v>
+        <v>1215700</v>
       </c>
       <c r="E83" s="3">
-        <v>1193200</v>
+        <v>1316100</v>
       </c>
       <c r="F83" s="3">
-        <v>999900</v>
+        <v>1129500</v>
       </c>
       <c r="G83" s="3">
-        <v>842400</v>
+        <v>946500</v>
       </c>
       <c r="H83" s="3">
-        <v>718700</v>
+        <v>797400</v>
       </c>
       <c r="I83" s="3">
-        <v>621200</v>
+        <v>680300</v>
       </c>
       <c r="J83" s="3">
+        <v>588100</v>
+      </c>
+      <c r="K83" s="3">
         <v>589700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>611700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>684500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>761300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>708500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>725000</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3573,9 +3774,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3615,9 +3819,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3657,9 +3864,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3699,9 +3909,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3741,51 +3954,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>1771100</v>
+        <v>2851900</v>
       </c>
       <c r="E89" s="3">
-        <v>1206400</v>
+        <v>1676500</v>
       </c>
       <c r="F89" s="3">
-        <v>1556000</v>
+        <v>1141900</v>
       </c>
       <c r="G89" s="3">
-        <v>1498900</v>
+        <v>1472900</v>
       </c>
       <c r="H89" s="3">
-        <v>945400</v>
+        <v>1418800</v>
       </c>
       <c r="I89" s="3">
-        <v>615400</v>
+        <v>894900</v>
       </c>
       <c r="J89" s="3">
+        <v>582600</v>
+      </c>
+      <c r="K89" s="3">
         <v>1079300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1114000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1218500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1166100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>990300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>500200</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3802,50 +4021,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1858300</v>
+        <v>-1394600</v>
       </c>
       <c r="E91" s="3">
-        <v>-1963600</v>
+        <v>-1759000</v>
       </c>
       <c r="F91" s="3">
-        <v>-1430200</v>
+        <v>-1858700</v>
       </c>
       <c r="G91" s="3">
-        <v>-1168900</v>
+        <v>-1353800</v>
       </c>
       <c r="H91" s="3">
-        <v>-1170000</v>
+        <v>-1106500</v>
       </c>
       <c r="I91" s="3">
-        <v>-1203800</v>
+        <v>-1107500</v>
       </c>
       <c r="J91" s="3">
+        <v>-1139500</v>
+      </c>
+      <c r="K91" s="3">
         <v>-1129800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1181000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-874500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-628400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-778200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-900900</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3885,9 +4108,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3927,51 +4153,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1579900</v>
+        <v>-1381900</v>
       </c>
       <c r="E94" s="3">
-        <v>-1897600</v>
+        <v>-1495500</v>
       </c>
       <c r="F94" s="3">
-        <v>-1559800</v>
+        <v>-1796300</v>
       </c>
       <c r="G94" s="3">
-        <v>-282800</v>
+        <v>-1476400</v>
       </c>
       <c r="H94" s="3">
-        <v>-944800</v>
+        <v>-267700</v>
       </c>
       <c r="I94" s="3">
-        <v>-1658700</v>
+        <v>-894300</v>
       </c>
       <c r="J94" s="3">
+        <v>-1570100</v>
+      </c>
+      <c r="K94" s="3">
         <v>-479300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1033300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1086000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-507800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-819500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-270300</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3988,50 +4220,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-250700</v>
+        <v>-268900</v>
       </c>
       <c r="E96" s="3">
-        <v>-161700</v>
+        <v>-237300</v>
       </c>
       <c r="F96" s="3">
-        <v>-153300</v>
+        <v>-153000</v>
       </c>
       <c r="G96" s="3">
-        <v>-144700</v>
+        <v>-145100</v>
       </c>
       <c r="H96" s="3">
-        <v>-127700</v>
+        <v>-137000</v>
       </c>
       <c r="I96" s="3">
+        <v>-120900</v>
+      </c>
+      <c r="J96" s="3">
+        <v>-96600</v>
+      </c>
+      <c r="K96" s="3">
         <v>-102000</v>
       </c>
-      <c r="J96" s="3">
-        <v>-102000</v>
-      </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-101900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-85900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-69200</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-91500</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-93300</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4071,9 +4307,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4113,9 +4352,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4155,133 +4397,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>100700</v>
+        <v>-933800</v>
       </c>
       <c r="E100" s="3">
-        <v>766600</v>
+        <v>95400</v>
       </c>
       <c r="F100" s="3">
-        <v>142100</v>
+        <v>725700</v>
       </c>
       <c r="G100" s="3">
-        <v>-820700</v>
+        <v>134500</v>
       </c>
       <c r="H100" s="3">
-        <v>63600</v>
+        <v>-776900</v>
       </c>
       <c r="I100" s="3">
-        <v>742000</v>
+        <v>60200</v>
       </c>
       <c r="J100" s="3">
+        <v>702400</v>
+      </c>
+      <c r="K100" s="3">
         <v>-254500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>215400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-300600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-514000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>40000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>116900</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>158600</v>
+        <v>381300</v>
       </c>
       <c r="E101" s="3">
-        <v>322000</v>
+        <v>150100</v>
       </c>
       <c r="F101" s="3">
-        <v>183000</v>
+        <v>304800</v>
       </c>
       <c r="G101" s="3">
-        <v>-101900</v>
+        <v>173200</v>
       </c>
       <c r="H101" s="3">
+        <v>-96400</v>
+      </c>
+      <c r="I101" s="3">
         <v>100</v>
       </c>
-      <c r="I101" s="3">
-        <v>-40900</v>
-      </c>
       <c r="J101" s="3">
+        <v>-38700</v>
+      </c>
+      <c r="K101" s="3">
         <v>-42800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-146400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>289700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>196100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>213500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-4000</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>450500</v>
+        <v>917500</v>
       </c>
       <c r="E102" s="3">
-        <v>397300</v>
+        <v>426500</v>
       </c>
       <c r="F102" s="3">
-        <v>321300</v>
+        <v>376100</v>
       </c>
       <c r="G102" s="3">
-        <v>293500</v>
+        <v>304100</v>
       </c>
       <c r="H102" s="3">
-        <v>64400</v>
+        <v>277800</v>
       </c>
       <c r="I102" s="3">
-        <v>-342100</v>
+        <v>60900</v>
       </c>
       <c r="J102" s="3">
+        <v>-323900</v>
+      </c>
+      <c r="K102" s="3">
         <v>302800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>149700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>121600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>340400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>424200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>342800</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/TTDKY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TTDKY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
   <si>
     <t>TTDKY</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>13422700</v>
+        <v>14937500</v>
       </c>
       <c r="E8" s="3">
-        <v>13913600</v>
+        <v>15483800</v>
       </c>
       <c r="F8" s="3">
-        <v>12135600</v>
+        <v>13505100</v>
       </c>
       <c r="G8" s="3">
-        <v>9436100</v>
+        <v>10501000</v>
       </c>
       <c r="H8" s="3">
-        <v>8696200</v>
+        <v>9677600</v>
       </c>
       <c r="I8" s="3">
-        <v>8815900</v>
+        <v>9810800</v>
       </c>
       <c r="J8" s="3">
-        <v>8113700</v>
+        <v>9029400</v>
       </c>
       <c r="K8" s="3">
         <v>7941500</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>9575500</v>
+        <v>10656100</v>
       </c>
       <c r="E9" s="3">
-        <v>10184400</v>
+        <v>11333700</v>
       </c>
       <c r="F9" s="3">
-        <v>8538200</v>
+        <v>9501800</v>
       </c>
       <c r="G9" s="3">
-        <v>6714400</v>
+        <v>7472100</v>
       </c>
       <c r="H9" s="3">
-        <v>6123000</v>
+        <v>6814000</v>
       </c>
       <c r="I9" s="3">
-        <v>6286300</v>
+        <v>6995800</v>
       </c>
       <c r="J9" s="3">
-        <v>5924000</v>
+        <v>6592500</v>
       </c>
       <c r="K9" s="3">
         <v>5769100</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>3847300</v>
+        <v>4281400</v>
       </c>
       <c r="E10" s="3">
-        <v>3729300</v>
+        <v>4150100</v>
       </c>
       <c r="F10" s="3">
-        <v>3597400</v>
+        <v>4003300</v>
       </c>
       <c r="G10" s="3">
-        <v>2721700</v>
+        <v>3028800</v>
       </c>
       <c r="H10" s="3">
-        <v>2573200</v>
+        <v>2863600</v>
       </c>
       <c r="I10" s="3">
-        <v>2529600</v>
+        <v>2815000</v>
       </c>
       <c r="J10" s="3">
-        <v>2189800</v>
+        <v>2436900</v>
       </c>
       <c r="K10" s="3">
         <v>2172400</v>
@@ -969,20 +969,20 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-8300</v>
       </c>
       <c r="E14" s="3">
-        <v>-9700</v>
+        <v>-10700</v>
       </c>
       <c r="F14" s="3">
-        <v>-44300</v>
+        <v>-49300</v>
       </c>
       <c r="G14" s="3">
-        <v>11100</v>
+        <v>12400</v>
       </c>
       <c r="H14" s="3">
-        <v>126900</v>
+        <v>141300</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>12319700</v>
+        <v>13710000</v>
       </c>
       <c r="E17" s="3">
-        <v>12836500</v>
+        <v>14285100</v>
       </c>
       <c r="F17" s="3">
-        <v>11071500</v>
+        <v>12321000</v>
       </c>
       <c r="G17" s="3">
-        <v>8722700</v>
+        <v>9707100</v>
       </c>
       <c r="H17" s="3">
-        <v>8080100</v>
+        <v>8992000</v>
       </c>
       <c r="I17" s="3">
-        <v>8128000</v>
+        <v>9045300</v>
       </c>
       <c r="J17" s="3">
-        <v>7541500</v>
+        <v>8392600</v>
       </c>
       <c r="K17" s="3">
         <v>6535100</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1103100</v>
+        <v>1227500</v>
       </c>
       <c r="E18" s="3">
-        <v>1077100</v>
+        <v>1198700</v>
       </c>
       <c r="F18" s="3">
-        <v>1064000</v>
+        <v>1184100</v>
       </c>
       <c r="G18" s="3">
-        <v>713400</v>
+        <v>793900</v>
       </c>
       <c r="H18" s="3">
-        <v>616100</v>
+        <v>685600</v>
       </c>
       <c r="I18" s="3">
-        <v>687900</v>
+        <v>765500</v>
       </c>
       <c r="J18" s="3">
-        <v>572200</v>
+        <v>636800</v>
       </c>
       <c r="K18" s="3">
         <v>1406400</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>40500</v>
+        <v>149100</v>
       </c>
       <c r="E20" s="3">
-        <v>62000</v>
+        <v>69000</v>
       </c>
       <c r="F20" s="3">
-        <v>81800</v>
+        <v>91100</v>
       </c>
       <c r="G20" s="3">
-        <v>93800</v>
+        <v>104400</v>
       </c>
       <c r="H20" s="3">
-        <v>19000</v>
+        <v>21200</v>
       </c>
       <c r="I20" s="3">
-        <v>75800</v>
+        <v>84400</v>
       </c>
       <c r="J20" s="3">
-        <v>29200</v>
+        <v>32500</v>
       </c>
       <c r="K20" s="3">
         <v>43700</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2357300</v>
+        <v>2720000</v>
       </c>
       <c r="E21" s="3">
-        <v>2453200</v>
+        <v>2722000</v>
       </c>
       <c r="F21" s="3">
-        <v>2273600</v>
+        <v>2523300</v>
       </c>
       <c r="G21" s="3">
-        <v>1752200</v>
+        <v>1944200</v>
       </c>
       <c r="H21" s="3">
-        <v>1431300</v>
+        <v>1587900</v>
       </c>
       <c r="I21" s="3">
-        <v>1443000</v>
+        <v>1601700</v>
       </c>
       <c r="J21" s="3">
-        <v>1188600</v>
+        <v>1319100</v>
       </c>
       <c r="K21" s="3">
         <v>2042400</v>
@@ -1274,26 +1274,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>104100</v>
       </c>
       <c r="E22" s="3">
-        <v>72300</v>
+        <v>80400</v>
       </c>
       <c r="F22" s="3">
-        <v>45400</v>
+        <v>50500</v>
       </c>
       <c r="G22" s="3">
-        <v>59000</v>
+        <v>65700</v>
       </c>
       <c r="H22" s="3">
-        <v>23400</v>
+        <v>26100</v>
       </c>
       <c r="I22" s="3">
-        <v>26500</v>
+        <v>29500</v>
       </c>
       <c r="J22" s="3">
-        <v>28500</v>
+        <v>31700</v>
       </c>
       <c r="K22" s="3">
         <v>23100</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1143600</v>
+        <v>1272600</v>
       </c>
       <c r="E23" s="3">
-        <v>1066900</v>
+        <v>1187300</v>
       </c>
       <c r="F23" s="3">
-        <v>1100500</v>
+        <v>1224700</v>
       </c>
       <c r="G23" s="3">
-        <v>748100</v>
+        <v>832600</v>
       </c>
       <c r="H23" s="3">
-        <v>611700</v>
+        <v>680700</v>
       </c>
       <c r="I23" s="3">
-        <v>737200</v>
+        <v>820400</v>
       </c>
       <c r="J23" s="3">
-        <v>573000</v>
+        <v>637700</v>
       </c>
       <c r="K23" s="3">
         <v>1427000</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>338800</v>
+        <v>377100</v>
       </c>
       <c r="E24" s="3">
-        <v>337600</v>
+        <v>375700</v>
       </c>
       <c r="F24" s="3">
-        <v>259500</v>
+        <v>288800</v>
       </c>
       <c r="G24" s="3">
-        <v>272400</v>
+        <v>303200</v>
       </c>
       <c r="H24" s="3">
-        <v>247000</v>
+        <v>274900</v>
       </c>
       <c r="I24" s="3">
-        <v>210600</v>
+        <v>234300</v>
       </c>
       <c r="J24" s="3">
-        <v>164800</v>
+        <v>183400</v>
       </c>
       <c r="K24" s="3">
         <v>445900</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>804700</v>
+        <v>895600</v>
       </c>
       <c r="E26" s="3">
-        <v>729200</v>
+        <v>811500</v>
       </c>
       <c r="F26" s="3">
-        <v>841000</v>
+        <v>935900</v>
       </c>
       <c r="G26" s="3">
-        <v>475700</v>
+        <v>529400</v>
       </c>
       <c r="H26" s="3">
-        <v>364700</v>
+        <v>405800</v>
       </c>
       <c r="I26" s="3">
-        <v>526700</v>
+        <v>586100</v>
       </c>
       <c r="J26" s="3">
-        <v>408200</v>
+        <v>454200</v>
       </c>
       <c r="K26" s="3">
         <v>981100</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>795500</v>
+        <v>885300</v>
       </c>
       <c r="E27" s="3">
-        <v>728500</v>
+        <v>810700</v>
       </c>
       <c r="F27" s="3">
-        <v>837700</v>
+        <v>932200</v>
       </c>
       <c r="G27" s="3">
-        <v>477300</v>
+        <v>531200</v>
       </c>
       <c r="H27" s="3">
-        <v>368600</v>
+        <v>410200</v>
       </c>
       <c r="I27" s="3">
-        <v>524500</v>
+        <v>583700</v>
       </c>
       <c r="J27" s="3">
-        <v>404900</v>
+        <v>450600</v>
       </c>
       <c r="K27" s="3">
         <v>978000</v>
@@ -1608,7 +1608,7 @@
         <v>8</v>
       </c>
       <c r="J29" s="3">
-        <v>-22400</v>
+        <v>-24900</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-40500</v>
+        <v>-149100</v>
       </c>
       <c r="E32" s="3">
-        <v>-62000</v>
+        <v>-69000</v>
       </c>
       <c r="F32" s="3">
-        <v>-81800</v>
+        <v>-91100</v>
       </c>
       <c r="G32" s="3">
-        <v>-93800</v>
+        <v>-104400</v>
       </c>
       <c r="H32" s="3">
-        <v>-19000</v>
+        <v>-21200</v>
       </c>
       <c r="I32" s="3">
-        <v>-75800</v>
+        <v>-84400</v>
       </c>
       <c r="J32" s="3">
-        <v>-29200</v>
+        <v>-32500</v>
       </c>
       <c r="K32" s="3">
         <v>-43700</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>795500</v>
+        <v>885300</v>
       </c>
       <c r="E33" s="3">
-        <v>728500</v>
+        <v>810700</v>
       </c>
       <c r="F33" s="3">
-        <v>837700</v>
+        <v>932200</v>
       </c>
       <c r="G33" s="3">
-        <v>477300</v>
+        <v>531200</v>
       </c>
       <c r="H33" s="3">
-        <v>368600</v>
+        <v>410200</v>
       </c>
       <c r="I33" s="3">
-        <v>524500</v>
+        <v>583700</v>
       </c>
       <c r="J33" s="3">
-        <v>382500</v>
+        <v>425600</v>
       </c>
       <c r="K33" s="3">
         <v>978000</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>795500</v>
+        <v>885300</v>
       </c>
       <c r="E35" s="3">
-        <v>728500</v>
+        <v>810700</v>
       </c>
       <c r="F35" s="3">
-        <v>837700</v>
+        <v>932200</v>
       </c>
       <c r="G35" s="3">
-        <v>477300</v>
+        <v>531200</v>
       </c>
       <c r="H35" s="3">
-        <v>368600</v>
+        <v>410200</v>
       </c>
       <c r="I35" s="3">
-        <v>524500</v>
+        <v>583700</v>
       </c>
       <c r="J35" s="3">
-        <v>382500</v>
+        <v>425600</v>
       </c>
       <c r="K35" s="3">
         <v>978000</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4147000</v>
+        <v>4615000</v>
       </c>
       <c r="E41" s="3">
-        <v>3229500</v>
+        <v>3593900</v>
       </c>
       <c r="F41" s="3">
-        <v>2803000</v>
+        <v>3119300</v>
       </c>
       <c r="G41" s="3">
-        <v>2426900</v>
+        <v>2700700</v>
       </c>
       <c r="H41" s="3">
-        <v>2122700</v>
+        <v>2362300</v>
       </c>
       <c r="I41" s="3">
-        <v>1844900</v>
+        <v>2053100</v>
       </c>
       <c r="J41" s="3">
-        <v>1784000</v>
+        <v>1985300</v>
       </c>
       <c r="K41" s="3">
         <v>2226800</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>300200</v>
+        <v>334100</v>
       </c>
       <c r="E42" s="3">
-        <v>332700</v>
+        <v>370200</v>
       </c>
       <c r="F42" s="3">
-        <v>427100</v>
+        <v>475300</v>
       </c>
       <c r="G42" s="3">
-        <v>902400</v>
+        <v>1004200</v>
       </c>
       <c r="H42" s="3">
-        <v>207700</v>
+        <v>231100</v>
       </c>
       <c r="I42" s="3">
-        <v>258800</v>
+        <v>288000</v>
       </c>
       <c r="J42" s="3">
-        <v>278600</v>
+        <v>310000</v>
       </c>
       <c r="K42" s="3">
         <v>378300</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3592700</v>
+        <v>4197800</v>
       </c>
       <c r="E43" s="3">
-        <v>3670900</v>
+        <v>4085200</v>
       </c>
       <c r="F43" s="3">
-        <v>3543200</v>
+        <v>3943100</v>
       </c>
       <c r="G43" s="3">
-        <v>5727000</v>
+        <v>6373300</v>
       </c>
       <c r="H43" s="3">
-        <v>2037400</v>
+        <v>2267300</v>
       </c>
       <c r="I43" s="3">
-        <v>2009200</v>
+        <v>2236000</v>
       </c>
       <c r="J43" s="3">
-        <v>1978300</v>
+        <v>2201600</v>
       </c>
       <c r="K43" s="3">
         <v>1759600</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2590800</v>
+        <v>2883200</v>
       </c>
       <c r="E44" s="3">
-        <v>2826300</v>
+        <v>3145300</v>
       </c>
       <c r="F44" s="3">
-        <v>2788100</v>
+        <v>3102700</v>
       </c>
       <c r="G44" s="3">
-        <v>3682500</v>
+        <v>4098100</v>
       </c>
       <c r="H44" s="3">
-        <v>1508600</v>
+        <v>1678800</v>
       </c>
       <c r="I44" s="3">
-        <v>1447600</v>
+        <v>1610900</v>
       </c>
       <c r="J44" s="3">
-        <v>1324100</v>
+        <v>1473500</v>
       </c>
       <c r="K44" s="3">
         <v>1041300</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>393700</v>
+        <v>238500</v>
       </c>
       <c r="E45" s="3">
-        <v>195200</v>
+        <v>217300</v>
       </c>
       <c r="F45" s="3">
-        <v>220200</v>
+        <v>245100</v>
       </c>
       <c r="G45" s="3">
-        <v>556300</v>
+        <v>619100</v>
       </c>
       <c r="H45" s="3">
-        <v>289800</v>
+        <v>322500</v>
       </c>
       <c r="I45" s="3">
-        <v>324900</v>
+        <v>361600</v>
       </c>
       <c r="J45" s="3">
-        <v>376600</v>
+        <v>419100</v>
       </c>
       <c r="K45" s="3">
         <v>431700</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>11024500</v>
+        <v>12268600</v>
       </c>
       <c r="E46" s="3">
-        <v>10254600</v>
+        <v>11411900</v>
       </c>
       <c r="F46" s="3">
-        <v>9781600</v>
+        <v>10885500</v>
       </c>
       <c r="G46" s="3">
-        <v>7853000</v>
+        <v>8739200</v>
       </c>
       <c r="H46" s="3">
-        <v>6166200</v>
+        <v>6862000</v>
       </c>
       <c r="I46" s="3">
-        <v>5885500</v>
+        <v>6549600</v>
       </c>
       <c r="J46" s="3">
-        <v>5741600</v>
+        <v>6389500</v>
       </c>
       <c r="K46" s="3">
         <v>5837800</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1412600</v>
+        <v>1572000</v>
       </c>
       <c r="E47" s="3">
-        <v>1139800</v>
+        <v>1268500</v>
       </c>
       <c r="F47" s="3">
-        <v>894600</v>
+        <v>995500</v>
       </c>
       <c r="G47" s="3">
-        <v>652800</v>
+        <v>726500</v>
       </c>
       <c r="H47" s="3">
-        <v>212000</v>
+        <v>235900</v>
       </c>
       <c r="I47" s="3">
-        <v>990900</v>
+        <v>1102700</v>
       </c>
       <c r="J47" s="3">
-        <v>990400</v>
+        <v>1102200</v>
       </c>
       <c r="K47" s="3">
         <v>1090700</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>6778200</v>
+        <v>7543100</v>
       </c>
       <c r="E48" s="3">
-        <v>6284100</v>
+        <v>6993300</v>
       </c>
       <c r="F48" s="3">
-        <v>6349400</v>
+        <v>7066000</v>
       </c>
       <c r="G48" s="3">
-        <v>10519800</v>
+        <v>11707000</v>
       </c>
       <c r="H48" s="3">
-        <v>4149300</v>
+        <v>4617600</v>
       </c>
       <c r="I48" s="3">
-        <v>3847800</v>
+        <v>4282100</v>
       </c>
       <c r="J48" s="3">
-        <v>3481200</v>
+        <v>3874100</v>
       </c>
       <c r="K48" s="3">
         <v>3131900</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1438700</v>
+        <v>1601000</v>
       </c>
       <c r="E49" s="3">
-        <v>1344600</v>
+        <v>1496400</v>
       </c>
       <c r="F49" s="3">
-        <v>1316700</v>
+        <v>1465300</v>
       </c>
       <c r="G49" s="3">
-        <v>2790600</v>
+        <v>3105500</v>
       </c>
       <c r="H49" s="3">
-        <v>1535600</v>
+        <v>1708900</v>
       </c>
       <c r="I49" s="3">
-        <v>1617200</v>
+        <v>1799800</v>
       </c>
       <c r="J49" s="3">
-        <v>1552800</v>
+        <v>1728100</v>
       </c>
       <c r="K49" s="3">
         <v>760600</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>1135700</v>
+        <v>1263900</v>
       </c>
       <c r="E52" s="3">
-        <v>1054800</v>
+        <v>1173900</v>
       </c>
       <c r="F52" s="3">
-        <v>1063400</v>
+        <v>1183400</v>
       </c>
       <c r="G52" s="3">
-        <v>428900</v>
+        <v>477300</v>
       </c>
       <c r="H52" s="3">
-        <v>335700</v>
+        <v>373500</v>
       </c>
       <c r="I52" s="3">
-        <v>370600</v>
+        <v>412500</v>
       </c>
       <c r="J52" s="3">
-        <v>389200</v>
+        <v>433100</v>
       </c>
       <c r="K52" s="3">
         <v>396700</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>21789600</v>
+        <v>24248700</v>
       </c>
       <c r="E54" s="3">
-        <v>20078000</v>
+        <v>22343900</v>
       </c>
       <c r="F54" s="3">
-        <v>19405700</v>
+        <v>21595700</v>
       </c>
       <c r="G54" s="3">
-        <v>15054600</v>
+        <v>16753600</v>
       </c>
       <c r="H54" s="3">
-        <v>12398800</v>
+        <v>13798000</v>
       </c>
       <c r="I54" s="3">
-        <v>12712000</v>
+        <v>14146600</v>
       </c>
       <c r="J54" s="3">
-        <v>12155200</v>
+        <v>13527000</v>
       </c>
       <c r="K54" s="3">
         <v>11217600</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2245400</v>
+        <v>2498800</v>
       </c>
       <c r="E57" s="3">
-        <v>2242200</v>
+        <v>2495200</v>
       </c>
       <c r="F57" s="3">
-        <v>2935600</v>
+        <v>3266900</v>
       </c>
       <c r="G57" s="3">
-        <v>4139000</v>
+        <v>4606100</v>
       </c>
       <c r="H57" s="3">
-        <v>1287600</v>
+        <v>1433000</v>
       </c>
       <c r="I57" s="3">
-        <v>1211500</v>
+        <v>1348200</v>
       </c>
       <c r="J57" s="3">
-        <v>1446900</v>
+        <v>1610200</v>
       </c>
       <c r="K57" s="3">
         <v>1190600</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1432500</v>
+        <v>1594200</v>
       </c>
       <c r="E58" s="3">
-        <v>1651200</v>
+        <v>1837500</v>
       </c>
       <c r="F58" s="3">
-        <v>1182600</v>
+        <v>1316000</v>
       </c>
       <c r="G58" s="3">
-        <v>4240800</v>
+        <v>4719400</v>
       </c>
       <c r="H58" s="3">
-        <v>1815900</v>
+        <v>2020900</v>
       </c>
       <c r="I58" s="3">
-        <v>1994300</v>
+        <v>2219400</v>
       </c>
       <c r="J58" s="3">
-        <v>1206700</v>
+        <v>1342900</v>
       </c>
       <c r="K58" s="3">
         <v>810100</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>2809900</v>
+        <v>3127000</v>
       </c>
       <c r="E59" s="3">
-        <v>2514100</v>
+        <v>2797900</v>
       </c>
       <c r="F59" s="3">
-        <v>2659600</v>
+        <v>2959800</v>
       </c>
       <c r="G59" s="3">
-        <v>4634100</v>
+        <v>5157100</v>
       </c>
       <c r="H59" s="3">
-        <v>1483000</v>
+        <v>1650400</v>
       </c>
       <c r="I59" s="3">
-        <v>1351600</v>
+        <v>1504100</v>
       </c>
       <c r="J59" s="3">
-        <v>1193700</v>
+        <v>1328500</v>
       </c>
       <c r="K59" s="3">
         <v>1218300</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>6487800</v>
+        <v>7219900</v>
       </c>
       <c r="E60" s="3">
-        <v>6407500</v>
+        <v>7130600</v>
       </c>
       <c r="F60" s="3">
-        <v>6777800</v>
+        <v>7542700</v>
       </c>
       <c r="G60" s="3">
-        <v>6560700</v>
+        <v>7301100</v>
       </c>
       <c r="H60" s="3">
-        <v>4586600</v>
+        <v>5104200</v>
       </c>
       <c r="I60" s="3">
-        <v>4557400</v>
+        <v>5071700</v>
       </c>
       <c r="J60" s="3">
-        <v>3847400</v>
+        <v>4281600</v>
       </c>
       <c r="K60" s="3">
         <v>3219000</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2942500</v>
+        <v>3274500</v>
       </c>
       <c r="E61" s="3">
-        <v>3147600</v>
+        <v>3502800</v>
       </c>
       <c r="F61" s="3">
-        <v>3154600</v>
+        <v>3510600</v>
       </c>
       <c r="G61" s="3">
-        <v>1181500</v>
+        <v>1314800</v>
       </c>
       <c r="H61" s="3">
-        <v>893600</v>
+        <v>994400</v>
       </c>
       <c r="I61" s="3">
-        <v>1325000</v>
+        <v>1474500</v>
       </c>
       <c r="J61" s="3">
-        <v>1875000</v>
+        <v>2086500</v>
       </c>
       <c r="K61" s="3">
         <v>1441900</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1418100</v>
+        <v>1578100</v>
       </c>
       <c r="E62" s="3">
-        <v>1189900</v>
+        <v>1324100</v>
       </c>
       <c r="F62" s="3">
-        <v>1155300</v>
+        <v>1285700</v>
       </c>
       <c r="G62" s="3">
-        <v>2112100</v>
+        <v>2350400</v>
       </c>
       <c r="H62" s="3">
-        <v>1504700</v>
+        <v>1674500</v>
       </c>
       <c r="I62" s="3">
-        <v>1191300</v>
+        <v>1325700</v>
       </c>
       <c r="J62" s="3">
-        <v>1129600</v>
+        <v>1257100</v>
       </c>
       <c r="K62" s="3">
         <v>1150400</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>10896900</v>
+        <v>12126600</v>
       </c>
       <c r="E66" s="3">
-        <v>10773100</v>
+        <v>11988900</v>
       </c>
       <c r="F66" s="3">
-        <v>11109700</v>
+        <v>12363500</v>
       </c>
       <c r="G66" s="3">
-        <v>8936700</v>
+        <v>9945200</v>
       </c>
       <c r="H66" s="3">
-        <v>7014300</v>
+        <v>7805900</v>
       </c>
       <c r="I66" s="3">
-        <v>7114900</v>
+        <v>7917800</v>
       </c>
       <c r="J66" s="3">
-        <v>6894100</v>
+        <v>7672100</v>
       </c>
       <c r="K66" s="3">
         <v>5868600</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>7265100</v>
+        <v>8085000</v>
       </c>
       <c r="E72" s="3">
-        <v>6729200</v>
+        <v>7488600</v>
       </c>
       <c r="F72" s="3">
-        <v>6219000</v>
+        <v>6920800</v>
       </c>
       <c r="G72" s="3">
-        <v>11979300</v>
+        <v>13331200</v>
       </c>
       <c r="H72" s="3">
-        <v>6484600</v>
+        <v>7216400</v>
       </c>
       <c r="I72" s="3">
-        <v>6252900</v>
+        <v>6958600</v>
       </c>
       <c r="J72" s="3">
-        <v>5869100</v>
+        <v>6531500</v>
       </c>
       <c r="K72" s="3">
         <v>5874700</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>10892800</v>
+        <v>12122100</v>
       </c>
       <c r="E76" s="3">
-        <v>9304900</v>
+        <v>10355000</v>
       </c>
       <c r="F76" s="3">
-        <v>8296000</v>
+        <v>9232300</v>
       </c>
       <c r="G76" s="3">
-        <v>6118000</v>
+        <v>6808400</v>
       </c>
       <c r="H76" s="3">
-        <v>5384400</v>
+        <v>5992100</v>
       </c>
       <c r="I76" s="3">
-        <v>5597100</v>
+        <v>6228800</v>
       </c>
       <c r="J76" s="3">
-        <v>5261200</v>
+        <v>5854900</v>
       </c>
       <c r="K76" s="3">
         <v>5349000</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>795500</v>
+        <v>885300</v>
       </c>
       <c r="E81" s="3">
-        <v>728500</v>
+        <v>810700</v>
       </c>
       <c r="F81" s="3">
-        <v>837700</v>
+        <v>932200</v>
       </c>
       <c r="G81" s="3">
-        <v>477300</v>
+        <v>531200</v>
       </c>
       <c r="H81" s="3">
-        <v>368600</v>
+        <v>410200</v>
       </c>
       <c r="I81" s="3">
-        <v>524500</v>
+        <v>583700</v>
       </c>
       <c r="J81" s="3">
-        <v>382500</v>
+        <v>425600</v>
       </c>
       <c r="K81" s="3">
         <v>978000</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1215700</v>
+        <v>1352900</v>
       </c>
       <c r="E83" s="3">
-        <v>1316100</v>
+        <v>1464600</v>
       </c>
       <c r="F83" s="3">
-        <v>1129500</v>
+        <v>1256900</v>
       </c>
       <c r="G83" s="3">
-        <v>946500</v>
+        <v>1053300</v>
       </c>
       <c r="H83" s="3">
-        <v>797400</v>
+        <v>887400</v>
       </c>
       <c r="I83" s="3">
-        <v>680300</v>
+        <v>757100</v>
       </c>
       <c r="J83" s="3">
-        <v>588100</v>
+        <v>654400</v>
       </c>
       <c r="K83" s="3">
         <v>589700</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2851900</v>
+        <v>3173700</v>
       </c>
       <c r="E89" s="3">
-        <v>1676500</v>
+        <v>1865700</v>
       </c>
       <c r="F89" s="3">
-        <v>1141900</v>
+        <v>1270800</v>
       </c>
       <c r="G89" s="3">
-        <v>1472900</v>
+        <v>1639100</v>
       </c>
       <c r="H89" s="3">
-        <v>1418800</v>
+        <v>1579000</v>
       </c>
       <c r="I89" s="3">
-        <v>894900</v>
+        <v>995900</v>
       </c>
       <c r="J89" s="3">
-        <v>582600</v>
+        <v>648300</v>
       </c>
       <c r="K89" s="3">
         <v>1079300</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1394600</v>
+        <v>-1552000</v>
       </c>
       <c r="E91" s="3">
-        <v>-1759000</v>
+        <v>-1957500</v>
       </c>
       <c r="F91" s="3">
-        <v>-1858700</v>
+        <v>-2068500</v>
       </c>
       <c r="G91" s="3">
-        <v>-1353800</v>
+        <v>-1506600</v>
       </c>
       <c r="H91" s="3">
-        <v>-1106500</v>
+        <v>-1231300</v>
       </c>
       <c r="I91" s="3">
-        <v>-1107500</v>
+        <v>-1232500</v>
       </c>
       <c r="J91" s="3">
-        <v>-1139500</v>
+        <v>-1268100</v>
       </c>
       <c r="K91" s="3">
         <v>-1129800</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1381900</v>
+        <v>-1537800</v>
       </c>
       <c r="E94" s="3">
-        <v>-1495500</v>
+        <v>-1664300</v>
       </c>
       <c r="F94" s="3">
-        <v>-1796300</v>
+        <v>-1999000</v>
       </c>
       <c r="G94" s="3">
-        <v>-1476400</v>
+        <v>-1643100</v>
       </c>
       <c r="H94" s="3">
-        <v>-267700</v>
+        <v>-297900</v>
       </c>
       <c r="I94" s="3">
-        <v>-894300</v>
+        <v>-995300</v>
       </c>
       <c r="J94" s="3">
-        <v>-1570100</v>
+        <v>-1747300</v>
       </c>
       <c r="K94" s="3">
         <v>-479300</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-268900</v>
+        <v>-299300</v>
       </c>
       <c r="E96" s="3">
-        <v>-237300</v>
+        <v>-264100</v>
       </c>
       <c r="F96" s="3">
-        <v>-153000</v>
+        <v>-170300</v>
       </c>
       <c r="G96" s="3">
-        <v>-145100</v>
+        <v>-161400</v>
       </c>
       <c r="H96" s="3">
-        <v>-137000</v>
+        <v>-152400</v>
       </c>
       <c r="I96" s="3">
-        <v>-120900</v>
+        <v>-134500</v>
       </c>
       <c r="J96" s="3">
-        <v>-96600</v>
+        <v>-107500</v>
       </c>
       <c r="K96" s="3">
         <v>-102000</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-933800</v>
+        <v>-1039200</v>
       </c>
       <c r="E100" s="3">
-        <v>95400</v>
+        <v>106100</v>
       </c>
       <c r="F100" s="3">
-        <v>725700</v>
+        <v>807600</v>
       </c>
       <c r="G100" s="3">
-        <v>134500</v>
+        <v>149700</v>
       </c>
       <c r="H100" s="3">
-        <v>-776900</v>
+        <v>-864600</v>
       </c>
       <c r="I100" s="3">
-        <v>60200</v>
+        <v>67000</v>
       </c>
       <c r="J100" s="3">
-        <v>702400</v>
+        <v>781600</v>
       </c>
       <c r="K100" s="3">
         <v>-254500</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>381300</v>
+        <v>424300</v>
       </c>
       <c r="E101" s="3">
-        <v>150100</v>
+        <v>167100</v>
       </c>
       <c r="F101" s="3">
-        <v>304800</v>
+        <v>339200</v>
       </c>
       <c r="G101" s="3">
-        <v>173200</v>
+        <v>192800</v>
       </c>
       <c r="H101" s="3">
-        <v>-96400</v>
+        <v>-107300</v>
       </c>
       <c r="I101" s="3">
         <v>100</v>
       </c>
       <c r="J101" s="3">
-        <v>-38700</v>
+        <v>-43000</v>
       </c>
       <c r="K101" s="3">
         <v>-42800</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>917500</v>
+        <v>1021100</v>
       </c>
       <c r="E102" s="3">
-        <v>426500</v>
+        <v>474600</v>
       </c>
       <c r="F102" s="3">
-        <v>376100</v>
+        <v>418600</v>
       </c>
       <c r="G102" s="3">
-        <v>304100</v>
+        <v>338500</v>
       </c>
       <c r="H102" s="3">
-        <v>277800</v>
+        <v>309100</v>
       </c>
       <c r="I102" s="3">
-        <v>60900</v>
+        <v>67800</v>
       </c>
       <c r="J102" s="3">
-        <v>-323900</v>
+        <v>-360400</v>
       </c>
       <c r="K102" s="3">
         <v>302800</v>

--- a/AAII_Financials/Yearly/TTDKY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TTDKY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
   <si>
     <t>TTDKY</t>
   </si>
@@ -726,25 +726,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>14937500</v>
+        <v>13909500</v>
       </c>
       <c r="E8" s="3">
-        <v>15483800</v>
+        <v>16405300</v>
       </c>
       <c r="F8" s="3">
-        <v>13505100</v>
+        <v>15663900</v>
       </c>
       <c r="G8" s="3">
-        <v>10501000</v>
+        <v>13372700</v>
       </c>
       <c r="H8" s="3">
-        <v>9677600</v>
+        <v>12667400</v>
       </c>
       <c r="I8" s="3">
-        <v>9810800</v>
+        <v>12470000</v>
       </c>
       <c r="J8" s="3">
-        <v>9029400</v>
+        <v>11974500</v>
       </c>
       <c r="K8" s="3">
         <v>7941500</v>
@@ -771,25 +771,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>10656100</v>
+        <v>9922700</v>
       </c>
       <c r="E9" s="3">
-        <v>11333700</v>
+        <v>12008200</v>
       </c>
       <c r="F9" s="3">
-        <v>9501800</v>
+        <v>11020600</v>
       </c>
       <c r="G9" s="3">
-        <v>7472100</v>
+        <v>9445700</v>
       </c>
       <c r="H9" s="3">
-        <v>6814000</v>
+        <v>8919100</v>
       </c>
       <c r="I9" s="3">
-        <v>6995800</v>
+        <v>8892000</v>
       </c>
       <c r="J9" s="3">
-        <v>6592500</v>
+        <v>8761500</v>
       </c>
       <c r="K9" s="3">
         <v>5769100</v>
@@ -816,25 +816,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>4281400</v>
+        <v>3986800</v>
       </c>
       <c r="E10" s="3">
-        <v>4150100</v>
+        <v>4397100</v>
       </c>
       <c r="F10" s="3">
-        <v>4003300</v>
+        <v>4643200</v>
       </c>
       <c r="G10" s="3">
-        <v>3028800</v>
+        <v>3927000</v>
       </c>
       <c r="H10" s="3">
-        <v>2863600</v>
+        <v>3748300</v>
       </c>
       <c r="I10" s="3">
-        <v>2815000</v>
+        <v>3578100</v>
       </c>
       <c r="J10" s="3">
-        <v>2436900</v>
+        <v>3212900</v>
       </c>
       <c r="K10" s="3">
         <v>2172400</v>
@@ -879,26 +879,26 @@
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>8</v>
+      <c r="D12" s="3">
+        <v>1248600</v>
+      </c>
+      <c r="E12" s="3">
+        <v>1350000</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1360800</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1148700</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1091900</v>
+      </c>
+      <c r="I12" s="3">
+        <v>1039200</v>
+      </c>
+      <c r="J12" s="3">
+        <v>974100</v>
       </c>
       <c r="K12" s="3" t="s">
         <v>8</v>
@@ -970,25 +970,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-8300</v>
+        <v>-73600</v>
       </c>
       <c r="E14" s="3">
-        <v>-10700</v>
+        <v>-25200</v>
       </c>
       <c r="F14" s="3">
-        <v>-49300</v>
+        <v>-4600</v>
       </c>
       <c r="G14" s="3">
-        <v>12400</v>
+        <v>-91500</v>
       </c>
       <c r="H14" s="3">
-        <v>141300</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
+        <v>-15800</v>
+      </c>
+      <c r="I14" s="3">
+        <v>-88800</v>
+      </c>
+      <c r="J14" s="3">
+        <v>2300</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1015,25 +1015,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>1259800</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1551800</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1457800</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>1268400</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>1161500</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>962300</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>867900</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1076,25 +1076,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13710000</v>
+        <v>12819100</v>
       </c>
       <c r="E17" s="3">
-        <v>14285100</v>
+        <v>15218800</v>
       </c>
       <c r="F17" s="3">
-        <v>12321000</v>
+        <v>14341000</v>
       </c>
       <c r="G17" s="3">
-        <v>9707100</v>
+        <v>12364200</v>
       </c>
       <c r="H17" s="3">
-        <v>8992000</v>
+        <v>11757800</v>
       </c>
       <c r="I17" s="3">
-        <v>9045300</v>
+        <v>11497000</v>
       </c>
       <c r="J17" s="3">
-        <v>8392600</v>
+        <v>11168200</v>
       </c>
       <c r="K17" s="3">
         <v>6535100</v>
@@ -1121,25 +1121,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1227500</v>
+        <v>1090400</v>
       </c>
       <c r="E18" s="3">
-        <v>1198700</v>
+        <v>1186500</v>
       </c>
       <c r="F18" s="3">
-        <v>1184100</v>
+        <v>1322900</v>
       </c>
       <c r="G18" s="3">
-        <v>793900</v>
+        <v>1008500</v>
       </c>
       <c r="H18" s="3">
-        <v>685600</v>
+        <v>909600</v>
       </c>
       <c r="I18" s="3">
-        <v>765500</v>
+        <v>973000</v>
       </c>
       <c r="J18" s="3">
-        <v>636800</v>
+        <v>806300</v>
       </c>
       <c r="K18" s="3">
         <v>1406400</v>
@@ -1185,25 +1185,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>149100</v>
+        <v>54700</v>
       </c>
       <c r="E20" s="3">
-        <v>69000</v>
+        <v>-13800</v>
       </c>
       <c r="F20" s="3">
-        <v>91100</v>
+        <v>-81200</v>
       </c>
       <c r="G20" s="3">
-        <v>104400</v>
+        <v>53800</v>
       </c>
       <c r="H20" s="3">
-        <v>21200</v>
+        <v>94700</v>
       </c>
       <c r="I20" s="3">
-        <v>84400</v>
+        <v>51500</v>
       </c>
       <c r="J20" s="3">
-        <v>32500</v>
+        <v>-23700</v>
       </c>
       <c r="K20" s="3">
         <v>43700</v>
@@ -1230,25 +1230,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2720000</v>
+        <v>2295400</v>
       </c>
       <c r="E21" s="3">
-        <v>2722000</v>
+        <v>2752100</v>
       </c>
       <c r="F21" s="3">
-        <v>2523300</v>
+        <v>2861900</v>
       </c>
       <c r="G21" s="3">
-        <v>1944200</v>
+        <v>2223000</v>
       </c>
       <c r="H21" s="3">
-        <v>1587900</v>
+        <v>1976400</v>
       </c>
       <c r="I21" s="3">
-        <v>1601700</v>
+        <v>1883900</v>
       </c>
       <c r="J21" s="3">
-        <v>1319100</v>
+        <v>1697900</v>
       </c>
       <c r="K21" s="3">
         <v>2042400</v>
@@ -1275,25 +1275,25 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>104100</v>
+        <v>96900</v>
       </c>
       <c r="E22" s="3">
-        <v>80400</v>
+        <v>85200</v>
       </c>
       <c r="F22" s="3">
-        <v>50500</v>
+        <v>58600</v>
       </c>
       <c r="G22" s="3">
-        <v>65700</v>
+        <v>31900</v>
       </c>
       <c r="H22" s="3">
-        <v>26100</v>
+        <v>34100</v>
       </c>
       <c r="I22" s="3">
-        <v>29500</v>
+        <v>37500</v>
       </c>
       <c r="J22" s="3">
-        <v>31700</v>
+        <v>42000</v>
       </c>
       <c r="K22" s="3">
         <v>23100</v>
@@ -1320,25 +1320,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>1272600</v>
+        <v>1185000</v>
       </c>
       <c r="E23" s="3">
-        <v>1187300</v>
+        <v>1257900</v>
       </c>
       <c r="F23" s="3">
-        <v>1224700</v>
+        <v>1420400</v>
       </c>
       <c r="G23" s="3">
-        <v>832600</v>
+        <v>1102200</v>
       </c>
       <c r="H23" s="3">
-        <v>680700</v>
+        <v>891000</v>
       </c>
       <c r="I23" s="3">
-        <v>820400</v>
+        <v>1042800</v>
       </c>
       <c r="J23" s="3">
-        <v>637700</v>
+        <v>845600</v>
       </c>
       <c r="K23" s="3">
         <v>1427000</v>
@@ -1365,25 +1365,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>377100</v>
+        <v>351100</v>
       </c>
       <c r="E24" s="3">
-        <v>375700</v>
+        <v>398100</v>
       </c>
       <c r="F24" s="3">
-        <v>288800</v>
+        <v>335000</v>
       </c>
       <c r="G24" s="3">
-        <v>303200</v>
+        <v>386100</v>
       </c>
       <c r="H24" s="3">
-        <v>274900</v>
+        <v>359800</v>
       </c>
       <c r="I24" s="3">
-        <v>234300</v>
+        <v>297800</v>
       </c>
       <c r="J24" s="3">
-        <v>183400</v>
+        <v>243200</v>
       </c>
       <c r="K24" s="3">
         <v>445900</v>
@@ -1455,25 +1455,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>895600</v>
+        <v>833900</v>
       </c>
       <c r="E26" s="3">
-        <v>811500</v>
+        <v>859800</v>
       </c>
       <c r="F26" s="3">
-        <v>935900</v>
+        <v>1085500</v>
       </c>
       <c r="G26" s="3">
-        <v>529400</v>
+        <v>716100</v>
       </c>
       <c r="H26" s="3">
-        <v>405800</v>
+        <v>531200</v>
       </c>
       <c r="I26" s="3">
-        <v>586100</v>
+        <v>745000</v>
       </c>
       <c r="J26" s="3">
-        <v>454200</v>
+        <v>602400</v>
       </c>
       <c r="K26" s="3">
         <v>981100</v>
@@ -1500,25 +1500,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>885300</v>
+        <v>824400</v>
       </c>
       <c r="E27" s="3">
-        <v>810700</v>
+        <v>859000</v>
       </c>
       <c r="F27" s="3">
-        <v>932200</v>
+        <v>1081200</v>
       </c>
       <c r="G27" s="3">
-        <v>531200</v>
+        <v>717400</v>
       </c>
       <c r="H27" s="3">
-        <v>410200</v>
+        <v>537000</v>
       </c>
       <c r="I27" s="3">
-        <v>583700</v>
+        <v>741900</v>
       </c>
       <c r="J27" s="3">
-        <v>450600</v>
+        <v>597500</v>
       </c>
       <c r="K27" s="3">
         <v>978000</v>
@@ -1589,26 +1589,26 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-24900</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-149100</v>
+        <v>-54700</v>
       </c>
       <c r="E32" s="3">
-        <v>-69000</v>
+        <v>13800</v>
       </c>
       <c r="F32" s="3">
-        <v>-91100</v>
+        <v>81200</v>
       </c>
       <c r="G32" s="3">
-        <v>-104400</v>
+        <v>-53800</v>
       </c>
       <c r="H32" s="3">
-        <v>-21200</v>
+        <v>-94700</v>
       </c>
       <c r="I32" s="3">
-        <v>-84400</v>
+        <v>-51500</v>
       </c>
       <c r="J32" s="3">
-        <v>-32500</v>
+        <v>23700</v>
       </c>
       <c r="K32" s="3">
         <v>-43700</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>885300</v>
+        <v>824300</v>
       </c>
       <c r="E33" s="3">
-        <v>810700</v>
+        <v>859000</v>
       </c>
       <c r="F33" s="3">
-        <v>932200</v>
+        <v>1081200</v>
       </c>
       <c r="G33" s="3">
-        <v>531200</v>
+        <v>717400</v>
       </c>
       <c r="H33" s="3">
-        <v>410200</v>
+        <v>537000</v>
       </c>
       <c r="I33" s="3">
-        <v>583700</v>
+        <v>741900</v>
       </c>
       <c r="J33" s="3">
-        <v>425600</v>
+        <v>597600</v>
       </c>
       <c r="K33" s="3">
         <v>978000</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>885300</v>
+        <v>824300</v>
       </c>
       <c r="E35" s="3">
-        <v>810700</v>
+        <v>859000</v>
       </c>
       <c r="F35" s="3">
-        <v>932200</v>
+        <v>1081200</v>
       </c>
       <c r="G35" s="3">
-        <v>531200</v>
+        <v>717400</v>
       </c>
       <c r="H35" s="3">
-        <v>410200</v>
+        <v>537000</v>
       </c>
       <c r="I35" s="3">
-        <v>583700</v>
+        <v>741900</v>
       </c>
       <c r="J35" s="3">
-        <v>425600</v>
+        <v>597600</v>
       </c>
       <c r="K35" s="3">
         <v>978000</v>
@@ -1993,25 +1993,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>4615000</v>
+        <v>4297400</v>
       </c>
       <c r="E41" s="3">
-        <v>3593900</v>
+        <v>3807800</v>
       </c>
       <c r="F41" s="3">
-        <v>3119300</v>
+        <v>3617900</v>
       </c>
       <c r="G41" s="3">
-        <v>2700700</v>
+        <v>3439300</v>
       </c>
       <c r="H41" s="3">
-        <v>2362300</v>
+        <v>3092100</v>
       </c>
       <c r="I41" s="3">
-        <v>2053100</v>
+        <v>2609600</v>
       </c>
       <c r="J41" s="3">
-        <v>1985300</v>
+        <v>2632900</v>
       </c>
       <c r="K41" s="3">
         <v>2226800</v>
@@ -2038,25 +2038,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>334100</v>
+        <v>0</v>
       </c>
       <c r="E42" s="3">
-        <v>370200</v>
+        <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>475300</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>1004200</v>
+        <v>596200</v>
       </c>
       <c r="H42" s="3">
-        <v>231100</v>
+        <v>302500</v>
       </c>
       <c r="I42" s="3">
-        <v>288000</v>
+        <v>366000</v>
       </c>
       <c r="J42" s="3">
-        <v>310000</v>
+        <v>411200</v>
       </c>
       <c r="K42" s="3">
         <v>378300</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4197800</v>
+        <v>3757200</v>
       </c>
       <c r="E43" s="3">
-        <v>4085200</v>
+        <v>4142500</v>
       </c>
       <c r="F43" s="3">
-        <v>3943100</v>
+        <v>4360000</v>
       </c>
       <c r="G43" s="3">
-        <v>6373300</v>
+        <v>3883000</v>
       </c>
       <c r="H43" s="3">
-        <v>2267300</v>
+        <v>2967800</v>
       </c>
       <c r="I43" s="3">
-        <v>2236000</v>
+        <v>2842100</v>
       </c>
       <c r="J43" s="3">
-        <v>2201600</v>
+        <v>2919700</v>
       </c>
       <c r="K43" s="3">
         <v>1759600</v>
@@ -2128,25 +2128,25 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>2883200</v>
+        <v>2684800</v>
       </c>
       <c r="E44" s="3">
-        <v>3145300</v>
+        <v>3332500</v>
       </c>
       <c r="F44" s="3">
-        <v>3102700</v>
+        <v>3598700</v>
       </c>
       <c r="G44" s="3">
-        <v>4098100</v>
+        <v>2611700</v>
       </c>
       <c r="H44" s="3">
-        <v>1678800</v>
+        <v>2197500</v>
       </c>
       <c r="I44" s="3">
-        <v>1610900</v>
+        <v>2047600</v>
       </c>
       <c r="J44" s="3">
-        <v>1473500</v>
+        <v>1954100</v>
       </c>
       <c r="K44" s="3">
         <v>1041300</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>238500</v>
+        <v>607800</v>
       </c>
       <c r="E45" s="3">
-        <v>217300</v>
+        <v>736600</v>
       </c>
       <c r="F45" s="3">
-        <v>245100</v>
+        <v>988200</v>
       </c>
       <c r="G45" s="3">
-        <v>619100</v>
+        <v>621600</v>
       </c>
       <c r="H45" s="3">
-        <v>322500</v>
+        <v>422100</v>
       </c>
       <c r="I45" s="3">
-        <v>361600</v>
+        <v>459600</v>
       </c>
       <c r="J45" s="3">
-        <v>419100</v>
+        <v>555800</v>
       </c>
       <c r="K45" s="3">
         <v>431700</v>
@@ -2218,25 +2218,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>12268600</v>
+        <v>11424300</v>
       </c>
       <c r="E46" s="3">
-        <v>11411900</v>
+        <v>12091000</v>
       </c>
       <c r="F46" s="3">
-        <v>10885500</v>
+        <v>12625600</v>
       </c>
       <c r="G46" s="3">
-        <v>8739200</v>
+        <v>11151900</v>
       </c>
       <c r="H46" s="3">
-        <v>6862000</v>
+        <v>8982000</v>
       </c>
       <c r="I46" s="3">
-        <v>6549600</v>
+        <v>8324900</v>
       </c>
       <c r="J46" s="3">
-        <v>6389500</v>
+        <v>8473600</v>
       </c>
       <c r="K46" s="3">
         <v>5837800</v>
@@ -2263,25 +2263,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1572000</v>
+        <v>2269300</v>
       </c>
       <c r="E47" s="3">
-        <v>1268500</v>
+        <v>2255200</v>
       </c>
       <c r="F47" s="3">
-        <v>995500</v>
+        <v>2197300</v>
       </c>
       <c r="G47" s="3">
-        <v>726500</v>
+        <v>560100</v>
       </c>
       <c r="H47" s="3">
-        <v>235900</v>
+        <v>473800</v>
       </c>
       <c r="I47" s="3">
-        <v>1102700</v>
+        <v>1607800</v>
       </c>
       <c r="J47" s="3">
-        <v>1102200</v>
+        <v>1743000</v>
       </c>
       <c r="K47" s="3">
         <v>1090700</v>
@@ -2308,25 +2308,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>7543100</v>
+        <v>7023900</v>
       </c>
       <c r="E48" s="3">
-        <v>6993300</v>
+        <v>7409500</v>
       </c>
       <c r="F48" s="3">
-        <v>7066000</v>
+        <v>8195500</v>
       </c>
       <c r="G48" s="3">
-        <v>11707000</v>
+        <v>7474700</v>
       </c>
       <c r="H48" s="3">
-        <v>4617600</v>
+        <v>6044200</v>
       </c>
       <c r="I48" s="3">
-        <v>4282100</v>
+        <v>5442700</v>
       </c>
       <c r="J48" s="3">
-        <v>3874100</v>
+        <v>5137600</v>
       </c>
       <c r="K48" s="3">
         <v>3131900</v>
@@ -2353,25 +2353,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1601000</v>
+        <v>1490800</v>
       </c>
       <c r="E49" s="3">
-        <v>1496400</v>
+        <v>1585400</v>
       </c>
       <c r="F49" s="3">
-        <v>1465300</v>
+        <v>1699500</v>
       </c>
       <c r="G49" s="3">
-        <v>3105500</v>
+        <v>2155300</v>
       </c>
       <c r="H49" s="3">
-        <v>1708900</v>
+        <v>2236900</v>
       </c>
       <c r="I49" s="3">
-        <v>1799800</v>
+        <v>2287600</v>
       </c>
       <c r="J49" s="3">
-        <v>1728100</v>
+        <v>2291700</v>
       </c>
       <c r="K49" s="3">
         <v>760600</v>
@@ -2487,26 +2487,26 @@
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>1263900</v>
-      </c>
-      <c r="E52" s="3">
-        <v>1173900</v>
-      </c>
-      <c r="F52" s="3">
-        <v>1183400</v>
-      </c>
-      <c r="G52" s="3">
-        <v>477300</v>
-      </c>
-      <c r="H52" s="3">
-        <v>373500</v>
-      </c>
-      <c r="I52" s="3">
-        <v>412500</v>
-      </c>
-      <c r="J52" s="3">
-        <v>433100</v>
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K52" s="3">
         <v>396700</v>
@@ -2578,25 +2578,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>24248700</v>
+        <v>22579800</v>
       </c>
       <c r="E54" s="3">
-        <v>22343900</v>
+        <v>23673600</v>
       </c>
       <c r="F54" s="3">
-        <v>21595700</v>
+        <v>25047800</v>
       </c>
       <c r="G54" s="3">
-        <v>16753600</v>
+        <v>21713000</v>
       </c>
       <c r="H54" s="3">
-        <v>13798000</v>
+        <v>18060800</v>
       </c>
       <c r="I54" s="3">
-        <v>14146600</v>
+        <v>17981000</v>
       </c>
       <c r="J54" s="3">
-        <v>13527000</v>
+        <v>17939000</v>
       </c>
       <c r="K54" s="3">
         <v>11217600</v>
@@ -2661,25 +2661,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>2498800</v>
+        <v>2326800</v>
       </c>
       <c r="E57" s="3">
-        <v>2495200</v>
+        <v>2643700</v>
       </c>
       <c r="F57" s="3">
-        <v>3266900</v>
+        <v>3789200</v>
       </c>
       <c r="G57" s="3">
-        <v>4606100</v>
+        <v>2932900</v>
       </c>
       <c r="H57" s="3">
-        <v>1433000</v>
+        <v>1875700</v>
       </c>
       <c r="I57" s="3">
-        <v>1348200</v>
+        <v>1713700</v>
       </c>
       <c r="J57" s="3">
-        <v>1610200</v>
+        <v>2135400</v>
       </c>
       <c r="K57" s="3">
         <v>1190600</v>
@@ -2706,25 +2706,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>1594200</v>
+        <v>1484500</v>
       </c>
       <c r="E58" s="3">
-        <v>1837500</v>
+        <v>1946900</v>
       </c>
       <c r="F58" s="3">
-        <v>1316000</v>
+        <v>1526400</v>
       </c>
       <c r="G58" s="3">
-        <v>4719400</v>
+        <v>3042600</v>
       </c>
       <c r="H58" s="3">
-        <v>2020900</v>
+        <v>2712600</v>
       </c>
       <c r="I58" s="3">
-        <v>2219400</v>
+        <v>2820900</v>
       </c>
       <c r="J58" s="3">
-        <v>1342900</v>
+        <v>1780900</v>
       </c>
       <c r="K58" s="3">
         <v>810100</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3127000</v>
+        <v>1124500</v>
       </c>
       <c r="E59" s="3">
-        <v>2797900</v>
+        <v>1293900</v>
       </c>
       <c r="F59" s="3">
-        <v>2959800</v>
+        <v>1835200</v>
       </c>
       <c r="G59" s="3">
-        <v>5157100</v>
+        <v>1308400</v>
       </c>
       <c r="H59" s="3">
-        <v>1650400</v>
+        <v>1035100</v>
       </c>
       <c r="I59" s="3">
-        <v>1504100</v>
+        <v>857300</v>
       </c>
       <c r="J59" s="3">
-        <v>1328500</v>
+        <v>913900</v>
       </c>
       <c r="K59" s="3">
         <v>1218300</v>
@@ -2796,25 +2796,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>7219900</v>
+        <v>6723000</v>
       </c>
       <c r="E60" s="3">
-        <v>7130600</v>
+        <v>7555000</v>
       </c>
       <c r="F60" s="3">
-        <v>7542700</v>
+        <v>8748400</v>
       </c>
       <c r="G60" s="3">
-        <v>7301100</v>
+        <v>9145400</v>
       </c>
       <c r="H60" s="3">
-        <v>5104200</v>
+        <v>6681100</v>
       </c>
       <c r="I60" s="3">
-        <v>5071700</v>
+        <v>6446300</v>
       </c>
       <c r="J60" s="3">
-        <v>4281600</v>
+        <v>5678000</v>
       </c>
       <c r="K60" s="3">
         <v>3219000</v>
@@ -2841,25 +2841,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>3274500</v>
+        <v>3049200</v>
       </c>
       <c r="E61" s="3">
-        <v>3502800</v>
+        <v>3711200</v>
       </c>
       <c r="F61" s="3">
-        <v>3510600</v>
+        <v>4071800</v>
       </c>
       <c r="G61" s="3">
-        <v>1314800</v>
+        <v>1673700</v>
       </c>
       <c r="H61" s="3">
-        <v>994400</v>
+        <v>1569500</v>
       </c>
       <c r="I61" s="3">
-        <v>1474500</v>
+        <v>1874200</v>
       </c>
       <c r="J61" s="3">
-        <v>2086500</v>
+        <v>2767100</v>
       </c>
       <c r="K61" s="3">
         <v>1441900</v>
@@ -2886,25 +2886,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1578100</v>
+        <v>213300</v>
       </c>
       <c r="E62" s="3">
-        <v>1324100</v>
+        <v>179000</v>
       </c>
       <c r="F62" s="3">
-        <v>1285700</v>
+        <v>152700</v>
       </c>
       <c r="G62" s="3">
-        <v>2350400</v>
+        <v>268000</v>
       </c>
       <c r="H62" s="3">
-        <v>1674500</v>
+        <v>239200</v>
       </c>
       <c r="I62" s="3">
-        <v>1325700</v>
+        <v>172200</v>
       </c>
       <c r="J62" s="3">
-        <v>1257100</v>
+        <v>155300</v>
       </c>
       <c r="K62" s="3">
         <v>1150400</v>
@@ -3066,25 +3066,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>12126600</v>
+        <v>11241700</v>
       </c>
       <c r="E66" s="3">
-        <v>11988900</v>
+        <v>12669100</v>
       </c>
       <c r="F66" s="3">
-        <v>12363500</v>
+        <v>14311500</v>
       </c>
       <c r="G66" s="3">
-        <v>9945200</v>
+        <v>12614400</v>
       </c>
       <c r="H66" s="3">
-        <v>7805900</v>
+        <v>10174700</v>
       </c>
       <c r="I66" s="3">
-        <v>7917800</v>
+        <v>10005600</v>
       </c>
       <c r="J66" s="3">
-        <v>7672100</v>
+        <v>10112300</v>
       </c>
       <c r="K66" s="3">
         <v>5868600</v>
@@ -3310,25 +3310,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>8085000</v>
+        <v>7528600</v>
       </c>
       <c r="E72" s="3">
-        <v>7488600</v>
+        <v>7934300</v>
       </c>
       <c r="F72" s="3">
-        <v>6920800</v>
+        <v>8027100</v>
       </c>
       <c r="G72" s="3">
-        <v>13331200</v>
+        <v>9678400</v>
       </c>
       <c r="H72" s="3">
-        <v>7216400</v>
+        <v>9445900</v>
       </c>
       <c r="I72" s="3">
-        <v>6958600</v>
+        <v>8844700</v>
       </c>
       <c r="J72" s="3">
-        <v>6531500</v>
+        <v>8661800</v>
       </c>
       <c r="K72" s="3">
         <v>5874700</v>
@@ -3490,25 +3490,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>12122100</v>
+        <v>11287800</v>
       </c>
       <c r="E76" s="3">
-        <v>10355000</v>
+        <v>10971200</v>
       </c>
       <c r="F76" s="3">
-        <v>9232300</v>
+        <v>10708000</v>
       </c>
       <c r="G76" s="3">
-        <v>6808400</v>
+        <v>9073700</v>
       </c>
       <c r="H76" s="3">
-        <v>5992100</v>
+        <v>7843300</v>
       </c>
       <c r="I76" s="3">
-        <v>6228800</v>
+        <v>7917100</v>
       </c>
       <c r="J76" s="3">
-        <v>5854900</v>
+        <v>7764500</v>
       </c>
       <c r="K76" s="3">
         <v>5349000</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>885300</v>
+        <v>824300</v>
       </c>
       <c r="E81" s="3">
-        <v>810700</v>
+        <v>859000</v>
       </c>
       <c r="F81" s="3">
-        <v>932200</v>
+        <v>1081200</v>
       </c>
       <c r="G81" s="3">
-        <v>531200</v>
+        <v>717400</v>
       </c>
       <c r="H81" s="3">
-        <v>410200</v>
+        <v>537000</v>
       </c>
       <c r="I81" s="3">
-        <v>583700</v>
+        <v>741900</v>
       </c>
       <c r="J81" s="3">
-        <v>425600</v>
+        <v>597600</v>
       </c>
       <c r="K81" s="3">
         <v>978000</v>
@@ -3694,25 +3694,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1352900</v>
+        <v>1259800</v>
       </c>
       <c r="E83" s="3">
-        <v>1464600</v>
+        <v>1551800</v>
       </c>
       <c r="F83" s="3">
-        <v>1256900</v>
+        <v>1457800</v>
       </c>
       <c r="G83" s="3">
-        <v>1053300</v>
+        <v>1268400</v>
       </c>
       <c r="H83" s="3">
-        <v>887400</v>
+        <v>1161500</v>
       </c>
       <c r="I83" s="3">
-        <v>757100</v>
+        <v>962300</v>
       </c>
       <c r="J83" s="3">
-        <v>654400</v>
+        <v>867900</v>
       </c>
       <c r="K83" s="3">
         <v>589700</v>
@@ -3964,25 +3964,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>3173700</v>
+        <v>2955300</v>
       </c>
       <c r="E89" s="3">
-        <v>1865700</v>
+        <v>1976700</v>
       </c>
       <c r="F89" s="3">
-        <v>1270800</v>
+        <v>1473900</v>
       </c>
       <c r="G89" s="3">
-        <v>1639100</v>
+        <v>2014600</v>
       </c>
       <c r="H89" s="3">
-        <v>1579000</v>
+        <v>2066800</v>
       </c>
       <c r="I89" s="3">
-        <v>995900</v>
+        <v>1265900</v>
       </c>
       <c r="J89" s="3">
-        <v>648300</v>
+        <v>859800</v>
       </c>
       <c r="K89" s="3">
         <v>1079300</v>
@@ -4028,25 +4028,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-1552000</v>
+        <v>-1445200</v>
       </c>
       <c r="E91" s="3">
-        <v>-1957500</v>
+        <v>-2074000</v>
       </c>
       <c r="F91" s="3">
-        <v>-2068500</v>
+        <v>-2399100</v>
       </c>
       <c r="G91" s="3">
-        <v>-1506600</v>
+        <v>-1920000</v>
       </c>
       <c r="H91" s="3">
-        <v>-1231300</v>
+        <v>-1611800</v>
       </c>
       <c r="I91" s="3">
-        <v>-1232500</v>
+        <v>-1566600</v>
       </c>
       <c r="J91" s="3">
-        <v>-1268100</v>
+        <v>-1681800</v>
       </c>
       <c r="K91" s="3">
         <v>-1129800</v>
@@ -4163,25 +4163,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1537800</v>
+        <v>-1432000</v>
       </c>
       <c r="E94" s="3">
-        <v>-1664300</v>
+        <v>-1763300</v>
       </c>
       <c r="F94" s="3">
-        <v>-1999000</v>
+        <v>-2318500</v>
       </c>
       <c r="G94" s="3">
-        <v>-1643100</v>
+        <v>-2093000</v>
       </c>
       <c r="H94" s="3">
-        <v>-297900</v>
+        <v>-390000</v>
       </c>
       <c r="I94" s="3">
-        <v>-995300</v>
+        <v>-1265000</v>
       </c>
       <c r="J94" s="3">
-        <v>-1747300</v>
+        <v>-2317200</v>
       </c>
       <c r="K94" s="3">
         <v>-479300</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-299300</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
-        <v>-264100</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3">
-        <v>-170300</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3">
-        <v>-161400</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-152400</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-134500</v>
+        <v>0</v>
       </c>
       <c r="J96" s="3">
-        <v>-107500</v>
+        <v>0</v>
       </c>
       <c r="K96" s="3">
         <v>-102000</v>
@@ -4407,25 +4407,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-1039200</v>
+        <v>-967700</v>
       </c>
       <c r="E100" s="3">
-        <v>106100</v>
+        <v>112400</v>
       </c>
       <c r="F100" s="3">
-        <v>807600</v>
+        <v>936700</v>
       </c>
       <c r="G100" s="3">
-        <v>149700</v>
+        <v>264000</v>
       </c>
       <c r="H100" s="3">
-        <v>-864600</v>
+        <v>-1131700</v>
       </c>
       <c r="I100" s="3">
-        <v>67000</v>
+        <v>85100</v>
       </c>
       <c r="J100" s="3">
-        <v>781600</v>
+        <v>1036600</v>
       </c>
       <c r="K100" s="3">
         <v>-254500</v>
@@ -4452,25 +4452,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>424300</v>
+        <v>395100</v>
       </c>
       <c r="E101" s="3">
-        <v>167100</v>
+        <v>177000</v>
       </c>
       <c r="F101" s="3">
-        <v>339200</v>
+        <v>393400</v>
       </c>
       <c r="G101" s="3">
-        <v>192800</v>
+        <v>245500</v>
       </c>
       <c r="H101" s="3">
-        <v>-107300</v>
+        <v>-140500</v>
       </c>
       <c r="I101" s="3">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="J101" s="3">
-        <v>-43000</v>
+        <v>-57100</v>
       </c>
       <c r="K101" s="3">
         <v>-42800</v>
@@ -4497,25 +4497,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1021100</v>
+        <v>950800</v>
       </c>
       <c r="E102" s="3">
-        <v>474600</v>
+        <v>502900</v>
       </c>
       <c r="F102" s="3">
-        <v>418600</v>
+        <v>485500</v>
       </c>
       <c r="G102" s="3">
-        <v>338500</v>
+        <v>431000</v>
       </c>
       <c r="H102" s="3">
-        <v>309100</v>
+        <v>404700</v>
       </c>
       <c r="I102" s="3">
-        <v>67800</v>
+        <v>86200</v>
       </c>
       <c r="J102" s="3">
-        <v>-360400</v>
+        <v>-478000</v>
       </c>
       <c r="K102" s="3">
         <v>302800</v>

--- a/AAII_Financials/Yearly/TTDKY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TTDKY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
   <si>
     <t>TTDKY</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44651</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44286</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43921</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43555</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43190</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42825</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42460</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42094</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41729</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41364</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40999</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>14723400</v>
+      </c>
+      <c r="E8" s="3">
         <v>13909500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>16405300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>15663900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>13372700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>12667400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>12470000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>11974500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>7941500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8469100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>9234200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>9018200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>7740800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>7363100</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>10128800</v>
+      </c>
+      <c r="E9" s="3">
         <v>9922700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12008200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>11020600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>9445700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>8919100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>8892000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>8761500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>5769100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>6108800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6843000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6994300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>6145600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5733700</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4594700</v>
+      </c>
+      <c r="E10" s="3">
         <v>3986800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4397100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4643200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3927000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>3748300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>3578100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>3212900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>2172400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>2360300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>2391300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>2023900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1595300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1629400</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,34 +886,35 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>1693400</v>
+      </c>
+      <c r="E12" s="3">
         <v>1248600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>1350000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>1360800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1148700</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>1091900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>1039200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>974100</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L12" s="3" t="s">
         <v>8</v>
@@ -918,9 +931,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -963,35 +979,38 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>-73600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-25200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-4600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-91500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-15800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-88800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2300</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
@@ -1002,42 +1021,45 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-60900</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>1310400</v>
+      </c>
+      <c r="E15" s="3">
         <v>1259800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1551800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1457800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1268400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1161500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>962300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>867900</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1053,9 +1075,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>13226300</v>
+      </c>
+      <c r="E17" s="3">
         <v>12819100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>15218800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>14341000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>12364200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>11757800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>11497000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>11168200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>6535100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>7782500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>8616200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>8682800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>7544000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>7194100</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1497100</v>
+      </c>
+      <c r="E18" s="3">
         <v>1090400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1186500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>1322900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1008500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>909600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>973000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>806300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1406400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>686600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>618100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>335400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>196800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>168900</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1179,233 +1211,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>54700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-13800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-81200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>53800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>94700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>51500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-23700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>43700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>11300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>43100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>60600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-31300</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>2807100</v>
+      </c>
+      <c r="E21" s="3">
         <v>2295400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>2752100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>2861900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2223000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1976400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1883900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1697900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2042400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1303800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1353700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1160600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>907300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>863400</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>89200</v>
+      </c>
+      <c r="E22" s="3">
         <v>96900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>85200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>58600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>31900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>34100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>37500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>42000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>23100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>22900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>25500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>31700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>25800</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>26900</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1588100</v>
+      </c>
+      <c r="E23" s="3">
         <v>1185000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1257900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1420400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1102200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>891000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1042800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>845600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1427000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>675000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>635600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>364300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>171400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>110700</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>450200</v>
+      </c>
+      <c r="E24" s="3">
         <v>351100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>398100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>335000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>386100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>359800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>297800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>243200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>445900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>185300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>185400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>164300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>130200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>103800</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1137800</v>
+      </c>
+      <c r="E26" s="3">
         <v>833900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>859800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1085500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>716100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>531200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>745000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>602400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>981100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>489700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>450200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>200000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>41200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>6900</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1116300</v>
+      </c>
+      <c r="E27" s="3">
         <v>824400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>859000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1081200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>717400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>537000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>741900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>597500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>978000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>476500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>421700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>182200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1610,8 +1670,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -1619,18 +1679,21 @@
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
+      <c r="N29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O29" s="3">
         <v>-33000</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-16400</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-54700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>13800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>81200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-53800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-94700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-51500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>23700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-43700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-11300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-43100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-60600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>31300</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1116300</v>
+      </c>
+      <c r="E33" s="3">
         <v>824300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>859000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1081200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>717400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>537000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>741900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>597600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>978000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>476500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>421700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>149200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-22200</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1116300</v>
+      </c>
+      <c r="E35" s="3">
         <v>824300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>859000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1081200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>717400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>537000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>741900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>597600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>978000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>476500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>421700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>149200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-22200</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44651</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44286</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43921</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43555</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43190</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42825</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42460</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42094</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41729</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41364</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40999</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,53 +2072,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4656500</v>
+      </c>
+      <c r="E41" s="3">
         <v>4297400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3807800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3617900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3439300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3092100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2609600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2632900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2226800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2098200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2261300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2297800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1942400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1509800</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2047,353 +2136,377 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>596200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>302500</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>366000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>411200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>378300</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>161400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>182500</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>79600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>97500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>65000</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>3933200</v>
+      </c>
+      <c r="E43" s="3">
         <v>3757200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4142500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4360000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3883000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2967800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2842100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2919700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1759600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1697000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2071600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1939900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1773000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1655000</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2738200</v>
+      </c>
+      <c r="E44" s="3">
         <v>2684800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3332500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3598700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2611700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2197500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2047600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1954100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1041300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1154900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1288100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1249300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1253200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1240600</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>938400</v>
+      </c>
+      <c r="E45" s="3">
         <v>607800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>736600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>988200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>621600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>422100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>459600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>555800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>431700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>334800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>510800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>417500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>484400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>463800</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12266300</v>
+      </c>
+      <c r="E46" s="3">
         <v>11424300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12091000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>12625600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>11151900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8982000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8324900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8473600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5837800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5446300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>6314300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5984100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5550600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4934200</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>281700</v>
+      </c>
+      <c r="E47" s="3">
         <v>2269300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2255200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2197300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>560100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>473800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1607800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1743000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1090700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>259700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>390100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>351800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>292800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>320500</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>7368100</v>
+      </c>
+      <c r="E48" s="3">
         <v>7023900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>7409500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>8195500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>7474700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>6044200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5442700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5137600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3131900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3584100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3644500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>3426100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3326000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3004200</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1429200</v>
+      </c>
+      <c r="E49" s="3">
         <v>1490800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1585400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1699500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2155300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2236900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2287600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2291700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>760600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>873400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>946900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1081800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1036600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>981500</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,14 +2597,17 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>8</v>
+      <c r="D52" s="3">
+        <v>1938900</v>
       </c>
       <c r="E52" s="3" t="s">
         <v>8</v>
@@ -2508,27 +2627,30 @@
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3">
         <v>396700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>498200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>682800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>510800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>425900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>457900</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>23649200</v>
+      </c>
+      <c r="E54" s="3">
         <v>22579800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>23673600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>25047800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>21713000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>18060800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17981000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17939000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11217600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10661800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>11978500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>11354600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10632000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>9698400</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,278 +2784,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2621100</v>
+      </c>
+      <c r="E57" s="3">
         <v>2326800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2643700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3789200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2932900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1875700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1713700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2135400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1190600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>828100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>951900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>876500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>772800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>792500</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1334200</v>
+      </c>
+      <c r="E58" s="3">
         <v>1484500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1946900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1526400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3042600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2712600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2820900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1780900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>810100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1432600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1167300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1551600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1801100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1291800</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>3380100</v>
+      </c>
+      <c r="E59" s="3">
         <v>1124500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1293900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1835200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1308400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1035100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>857300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>913900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1218300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1055900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1189400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>995800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>861600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>861900</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7335400</v>
+      </c>
+      <c r="E60" s="3">
         <v>6723000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7555000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8748400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>9145400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>6681100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>6446300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>5678000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3219000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3316600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3308600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3423800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3435400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2946200</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2728600</v>
+      </c>
+      <c r="E61" s="3">
         <v>3049200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>3711200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4071800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1673700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1569500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1874200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2767100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1441900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1035200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1121500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>894200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>886100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1174700</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>220700</v>
+      </c>
+      <c r="E62" s="3">
         <v>213300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>179000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>152700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>268000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>239200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>172200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>155300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1150400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1278000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1082600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1062000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1032700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>948600</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11553800</v>
+      </c>
+      <c r="E66" s="3">
         <v>11241700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12669100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>14311500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>12614400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10174700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10005600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10112300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5868600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5697900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5676000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5535000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5531000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5195000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3258,9 +3425,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,54 +3473,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>8504000</v>
+      </c>
+      <c r="E72" s="3">
         <v>7528600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7934300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>8027100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9678400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>9445900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>8844700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>8661800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>5874700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>5451700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>5892900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>5968400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>5843100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>5891000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>12020700</v>
+      </c>
+      <c r="E76" s="3">
         <v>11287800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>10971200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>10708000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>9073700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7843300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7917100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7764500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5349000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4963900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>6302500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5819600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5101000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4503400</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44651</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44286</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43921</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43555</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43190</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42825</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42460</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42094</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41729</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41364</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40999</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1116300</v>
+      </c>
+      <c r="E81" s="3">
         <v>824300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>859000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1081200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>717400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>537000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>741900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>597600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>978000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>476500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>421700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>149200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-22200</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1310400</v>
+      </c>
+      <c r="E83" s="3">
         <v>1259800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1551800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1457800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1268400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1161500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>962300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>867900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>589700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>611700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>684500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>761300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>708500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>725000</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2977300</v>
+      </c>
+      <c r="E89" s="3">
         <v>2955300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1976700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1473900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2014600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>2066800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1265900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>859800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>1079300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>1114000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1218500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1166100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>990300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>500200</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-1504500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-1445200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2074000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2399100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1920000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1611800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1566600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1681800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1129800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1181000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-874500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-628400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-778200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-900900</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-1635000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-1432000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1763300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2318500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2093000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-390000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1265000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2317200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-479300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1033300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1086000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-507800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-819500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-270300</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,13 +4453,14 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>0</v>
+        <v>324100</v>
       </c>
       <c r="E96" s="3">
         <v>0</v>
@@ -4248,26 +4481,29 @@
         <v>0</v>
       </c>
       <c r="K96" s="3">
+        <v>0</v>
+      </c>
+      <c r="L96" s="3">
         <v>-102000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-101900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-85900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-69200</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-91500</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-93300</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,142 +4642,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-957200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-967700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>112400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>936700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>264000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1131700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>85100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1036600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-254500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>215400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-300600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-514000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>40000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>116900</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-69100</v>
+      </c>
+      <c r="E101" s="3">
         <v>395100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>177000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>393400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>245500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-140500</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-57100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-42800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-146400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>289700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>196100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>213500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4000</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>315900</v>
+      </c>
+      <c r="E102" s="3">
         <v>950800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>502900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>485500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>431000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>404700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>86200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-478000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>302800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>149700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>121600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>340400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>424200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>342800</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/TTDKY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/TTDKY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="92">
   <si>
     <t>TTDKY</t>
   </si>
@@ -988,8 +988,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>-43800</v>
       </c>
       <c r="E14" s="3">
         <v>-73600</v>
@@ -1037,10 +1037,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>1310400</v>
+        <v>1176100</v>
       </c>
       <c r="E15" s="3">
-        <v>1259800</v>
+        <v>1141700</v>
       </c>
       <c r="F15" s="3">
         <v>1551800</v>
@@ -1102,10 +1102,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>13226300</v>
+        <v>13248700</v>
       </c>
       <c r="E17" s="3">
-        <v>12819100</v>
+        <v>12781200</v>
       </c>
       <c r="F17" s="3">
         <v>15218800</v>
@@ -1150,10 +1150,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1497100</v>
+        <v>1474700</v>
       </c>
       <c r="E18" s="3">
-        <v>1090400</v>
+        <v>1128300</v>
       </c>
       <c r="F18" s="3">
         <v>1186500</v>
@@ -1218,10 +1218,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>400</v>
+        <v>15200</v>
       </c>
       <c r="E20" s="3">
-        <v>54700</v>
+        <v>79800</v>
       </c>
       <c r="F20" s="3">
         <v>-13800</v>
@@ -1266,10 +1266,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>2807100</v>
+        <v>2635600</v>
       </c>
       <c r="E21" s="3">
-        <v>2295400</v>
+        <v>2190300</v>
       </c>
       <c r="F21" s="3">
         <v>2752100</v>
@@ -1314,7 +1314,7 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>89200</v>
+        <v>67300</v>
       </c>
       <c r="E22" s="3">
         <v>96900</v>
@@ -1794,10 +1794,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-400</v>
+        <v>-15200</v>
       </c>
       <c r="E32" s="3">
-        <v>-54700</v>
+        <v>-79800</v>
       </c>
       <c r="F32" s="3">
         <v>13800</v>
@@ -2175,10 +2175,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>3933200</v>
+        <v>4137600</v>
       </c>
       <c r="E43" s="3">
-        <v>3757200</v>
+        <v>3908900</v>
       </c>
       <c r="F43" s="3">
         <v>4142500</v>
@@ -2271,10 +2271,10 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>938400</v>
+        <v>653100</v>
       </c>
       <c r="E45" s="3">
-        <v>607800</v>
+        <v>456100</v>
       </c>
       <c r="F45" s="3">
         <v>736600</v>
@@ -2370,7 +2370,7 @@
         <v>281700</v>
       </c>
       <c r="E47" s="3">
-        <v>2269300</v>
+        <v>244600</v>
       </c>
       <c r="F47" s="3">
         <v>2255200</v>
@@ -2609,8 +2609,8 @@
       <c r="D52" s="3">
         <v>1938900</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>8</v>
+      <c r="E52" s="3">
+        <v>2024700</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>8</v>
@@ -2887,10 +2887,10 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>3380100</v>
+        <v>1302500</v>
       </c>
       <c r="E59" s="3">
-        <v>1124500</v>
+        <v>1069900</v>
       </c>
       <c r="F59" s="3">
         <v>1293900</v>
@@ -3892,10 +3892,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1310400</v>
+        <v>1216500</v>
       </c>
       <c r="E83" s="3">
-        <v>1259800</v>
+        <v>1166500</v>
       </c>
       <c r="F83" s="3">
         <v>1551800</v>
@@ -4463,7 +4463,7 @@
         <v>324100</v>
       </c>
       <c r="E96" s="3">
-        <v>0</v>
+        <v>278700</v>
       </c>
       <c r="F96" s="3">
         <v>0</v>
